--- a/docs/workbook-split/dateien/Forecast.xlsx
+++ b/docs/workbook-split/dateien/Forecast.xlsx
@@ -721,57 +721,46 @@
       <c r="C7" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="D7" s="1">
-        <f>IF(C7&lt;='[Steuerung.xlsx]Steuerung'!$F$8,"IST","FC")</f>
-        <v/>
-      </c>
-      <c r="E7" s="6">
-        <f>IF(AND(C7&lt;='[Steuerung.xlsx]Steuerung'!$F$8,COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,1)&gt;0),'[GuV.xlsx]GuV'!F7,SUMIFS('[D Finanzen.xlsx]D Finanzen'!$E$278:$E$301,'[D Finanzen.xlsx]D Finanzen'!$H$278:$H$301,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$A$278:$A$301,C7))</f>
-        <v/>
-      </c>
-      <c r="F7" s="6">
-        <f>IF(AND(C7&lt;='[Steuerung.xlsx]Steuerung'!$F$8,COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,1)&gt;0),'[GuV.xlsx]GuV'!F8,SUMIFS('[D Finanzen.xlsx]D Finanzen'!$F$278:$F$301,'[D Finanzen.xlsx]D Finanzen'!$H$278:$H$301,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$A$278:$A$301,C7))</f>
-        <v/>
-      </c>
-      <c r="G7" s="6">
-        <f>SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$506,'[FC Eingabe.xlsx]FC Eingabe'!$C$7:$C$506,'[Steuerung.xlsx]Steuerung'!$F$6,'[FC Eingabe.xlsx]FC Eingabe'!$D$7:$D$506,C7,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$506,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="H7" s="6">
-        <f>SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$506,'[FC Eingabe.xlsx]FC Eingabe'!$C$7:$C$506,'[Steuerung.xlsx]Steuerung'!$F$6,'[FC Eingabe.xlsx]FC Eingabe'!$D$7:$D$506,C7,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$506,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="I7" s="6">
-        <f>SUM(E7:H7)</f>
-        <v/>
-      </c>
-      <c r="J7" s="6">
-        <f>IF(AND(C7&lt;='[Steuerung.xlsx]Steuerung'!$F$8,COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,1)&gt;0),'[GuV.xlsx]GuV'!F20,SUMIFS('[D Finanzen.xlsx]D Finanzen'!$G$22:$G$33,'[D Finanzen.xlsx]D Finanzen'!$A$22:$A$33,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$22:$B$33,C7))</f>
-        <v/>
-      </c>
-      <c r="K7" s="6">
-        <f>SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$506,'[FC Eingabe.xlsx]FC Eingabe'!$C$7:$C$506,'[Steuerung.xlsx]Steuerung'!$F$6,'[FC Eingabe.xlsx]FC Eingabe'!$D$7:$D$506,C7,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$506,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="L7" s="6">
-        <f>J7+G7+H7-K7</f>
-        <v/>
-      </c>
-      <c r="M7" s="6">
-        <f>SUMIFS('[D Finanzen.xlsx]D Finanzen'!$D$182:$D$193,'[D Finanzen.xlsx]D Finanzen'!$A$182:$A$193,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$182:$B$193,C7)</f>
-        <v/>
-      </c>
-      <c r="N7" s="6">
-        <f>SUMIFS('[D Finanzen.xlsx]D Finanzen'!$G$182:$G$193,'[D Finanzen.xlsx]D Finanzen'!$A$182:$A$193,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$182:$B$193,C7)</f>
-        <v/>
-      </c>
-      <c r="O7" s="6">
-        <f>L7-N7</f>
-        <v/>
-      </c>
-      <c r="P7" s="7">
-        <f>IF(I7=0,"n.a.",L7/I7)</f>
-        <v/>
+      <c r="D7" s="1" t="inlineStr">
+        <is>
+          <t>IST</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>639565.45</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>1280847.26</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>1920412.71</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>294942.37</v>
+      </c>
+      <c r="K7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" s="6" t="n">
+        <v>294942.37</v>
+      </c>
+      <c r="M7" s="6" t="n">
+        <v>1416000</v>
+      </c>
+      <c r="N7" s="6" t="n">
+        <v>76000</v>
+      </c>
+      <c r="O7" s="6" t="n">
+        <v>218942.37</v>
+      </c>
+      <c r="P7" s="7" t="n">
+        <v>0.1535828046045373</v>
       </c>
       <c r="Q7" s="1" t="n"/>
     </row>
@@ -781,57 +770,46 @@
       <c r="C8" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="D8" s="1">
-        <f>IF(C8&lt;='[Steuerung.xlsx]Steuerung'!$F$8,"IST","FC")</f>
-        <v/>
-      </c>
-      <c r="E8" s="6">
-        <f>IF(AND(C8&lt;='[Steuerung.xlsx]Steuerung'!$F$8,COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,2)&gt;0),'[GuV.xlsx]GuV'!G7,SUMIFS('[D Finanzen.xlsx]D Finanzen'!$E$278:$E$301,'[D Finanzen.xlsx]D Finanzen'!$H$278:$H$301,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$A$278:$A$301,C8))</f>
-        <v/>
-      </c>
-      <c r="F8" s="6">
-        <f>IF(AND(C8&lt;='[Steuerung.xlsx]Steuerung'!$F$8,COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,2)&gt;0),'[GuV.xlsx]GuV'!G8,SUMIFS('[D Finanzen.xlsx]D Finanzen'!$F$278:$F$301,'[D Finanzen.xlsx]D Finanzen'!$H$278:$H$301,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$A$278:$A$301,C8))</f>
-        <v/>
-      </c>
-      <c r="G8" s="6">
-        <f>SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$506,'[FC Eingabe.xlsx]FC Eingabe'!$C$7:$C$506,'[Steuerung.xlsx]Steuerung'!$F$6,'[FC Eingabe.xlsx]FC Eingabe'!$D$7:$D$506,C8,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$506,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="H8" s="6">
-        <f>SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$506,'[FC Eingabe.xlsx]FC Eingabe'!$C$7:$C$506,'[Steuerung.xlsx]Steuerung'!$F$6,'[FC Eingabe.xlsx]FC Eingabe'!$D$7:$D$506,C8,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$506,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="I8" s="6">
-        <f>SUM(E8:H8)</f>
-        <v/>
-      </c>
-      <c r="J8" s="6">
-        <f>IF(AND(C8&lt;='[Steuerung.xlsx]Steuerung'!$F$8,COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,2)&gt;0),'[GuV.xlsx]GuV'!G20,SUMIFS('[D Finanzen.xlsx]D Finanzen'!$G$22:$G$33,'[D Finanzen.xlsx]D Finanzen'!$A$22:$A$33,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$22:$B$33,C8))</f>
-        <v/>
-      </c>
-      <c r="K8" s="6">
-        <f>SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$506,'[FC Eingabe.xlsx]FC Eingabe'!$C$7:$C$506,'[Steuerung.xlsx]Steuerung'!$F$6,'[FC Eingabe.xlsx]FC Eingabe'!$D$7:$D$506,C8,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$506,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="L8" s="6">
-        <f>J8+G8+H8-K8</f>
-        <v/>
-      </c>
-      <c r="M8" s="6">
-        <f>SUMIFS('[D Finanzen.xlsx]D Finanzen'!$D$182:$D$193,'[D Finanzen.xlsx]D Finanzen'!$A$182:$A$193,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$182:$B$193,C8)</f>
-        <v/>
-      </c>
-      <c r="N8" s="6">
-        <f>SUMIFS('[D Finanzen.xlsx]D Finanzen'!$G$182:$G$193,'[D Finanzen.xlsx]D Finanzen'!$A$182:$A$193,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$182:$B$193,C8)</f>
-        <v/>
-      </c>
-      <c r="O8" s="6">
-        <f>L8-N8</f>
-        <v/>
-      </c>
-      <c r="P8" s="7">
-        <f>IF(I8=0,"n.a.",L8/I8)</f>
-        <v/>
+      <c r="D8" s="1" t="inlineStr">
+        <is>
+          <t>IST</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>2777244.65</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>-200176.92</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>2577067.73</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>318570.76</v>
+      </c>
+      <c r="K8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="6" t="n">
+        <v>318570.76</v>
+      </c>
+      <c r="M8" s="6" t="n">
+        <v>1348000</v>
+      </c>
+      <c r="N8" s="6" t="n">
+        <v>25000</v>
+      </c>
+      <c r="O8" s="6" t="n">
+        <v>293570.76</v>
+      </c>
+      <c r="P8" s="7" t="n">
+        <v>0.1236175348794578</v>
       </c>
       <c r="Q8" s="1" t="n"/>
     </row>
@@ -841,57 +819,46 @@
       <c r="C9" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="D9" s="1">
-        <f>IF(C9&lt;='[Steuerung.xlsx]Steuerung'!$F$8,"IST","FC")</f>
-        <v/>
-      </c>
-      <c r="E9" s="6">
-        <f>IF(AND(C9&lt;='[Steuerung.xlsx]Steuerung'!$F$8,COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,3)&gt;0),'[GuV.xlsx]GuV'!H7,SUMIFS('[D Finanzen.xlsx]D Finanzen'!$E$278:$E$301,'[D Finanzen.xlsx]D Finanzen'!$H$278:$H$301,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$A$278:$A$301,C9))</f>
-        <v/>
-      </c>
-      <c r="F9" s="6">
-        <f>IF(AND(C9&lt;='[Steuerung.xlsx]Steuerung'!$F$8,COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,3)&gt;0),'[GuV.xlsx]GuV'!H8,SUMIFS('[D Finanzen.xlsx]D Finanzen'!$F$278:$F$301,'[D Finanzen.xlsx]D Finanzen'!$H$278:$H$301,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$A$278:$A$301,C9))</f>
-        <v/>
-      </c>
-      <c r="G9" s="6">
-        <f>SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$506,'[FC Eingabe.xlsx]FC Eingabe'!$C$7:$C$506,'[Steuerung.xlsx]Steuerung'!$F$6,'[FC Eingabe.xlsx]FC Eingabe'!$D$7:$D$506,C9,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$506,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="H9" s="6">
-        <f>SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$506,'[FC Eingabe.xlsx]FC Eingabe'!$C$7:$C$506,'[Steuerung.xlsx]Steuerung'!$F$6,'[FC Eingabe.xlsx]FC Eingabe'!$D$7:$D$506,C9,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$506,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="I9" s="6">
-        <f>SUM(E9:H9)</f>
-        <v/>
-      </c>
-      <c r="J9" s="6">
-        <f>IF(AND(C9&lt;='[Steuerung.xlsx]Steuerung'!$F$8,COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,3)&gt;0),'[GuV.xlsx]GuV'!H20,SUMIFS('[D Finanzen.xlsx]D Finanzen'!$G$22:$G$33,'[D Finanzen.xlsx]D Finanzen'!$A$22:$A$33,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$22:$B$33,C9))</f>
-        <v/>
-      </c>
-      <c r="K9" s="6">
-        <f>SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$506,'[FC Eingabe.xlsx]FC Eingabe'!$C$7:$C$506,'[Steuerung.xlsx]Steuerung'!$F$6,'[FC Eingabe.xlsx]FC Eingabe'!$D$7:$D$506,C9,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$506,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="L9" s="6">
-        <f>J9+G9+H9-K9</f>
-        <v/>
-      </c>
-      <c r="M9" s="6">
-        <f>SUMIFS('[D Finanzen.xlsx]D Finanzen'!$D$182:$D$193,'[D Finanzen.xlsx]D Finanzen'!$A$182:$A$193,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$182:$B$193,C9)</f>
-        <v/>
-      </c>
-      <c r="N9" s="6">
-        <f>SUMIFS('[D Finanzen.xlsx]D Finanzen'!$G$182:$G$193,'[D Finanzen.xlsx]D Finanzen'!$A$182:$A$193,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$182:$B$193,C9)</f>
-        <v/>
-      </c>
-      <c r="O9" s="6">
-        <f>L9-N9</f>
-        <v/>
-      </c>
-      <c r="P9" s="7">
-        <f>IF(I9=0,"n.a.",L9/I9)</f>
-        <v/>
+      <c r="D9" s="1" t="inlineStr">
+        <is>
+          <t>IST</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>1213541.38</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>1198671.49</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>2412212.87</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>23595.18</v>
+      </c>
+      <c r="K9" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" s="6" t="n">
+        <v>23595.18</v>
+      </c>
+      <c r="M9" s="6" t="n">
+        <v>1483000</v>
+      </c>
+      <c r="N9" s="6" t="n">
+        <v>127000</v>
+      </c>
+      <c r="O9" s="6" t="n">
+        <v>-103404.82</v>
+      </c>
+      <c r="P9" s="7" t="n">
+        <v>0.00978154966895604</v>
       </c>
       <c r="Q9" s="1" t="n"/>
     </row>
@@ -901,57 +868,46 @@
       <c r="C10" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="D10" s="1">
-        <f>IF(C10&lt;='[Steuerung.xlsx]Steuerung'!$F$8,"IST","FC")</f>
-        <v/>
-      </c>
-      <c r="E10" s="6">
-        <f>IF(AND(C10&lt;='[Steuerung.xlsx]Steuerung'!$F$8,COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,4)&gt;0),'[GuV.xlsx]GuV'!I7,SUMIFS('[D Finanzen.xlsx]D Finanzen'!$E$278:$E$301,'[D Finanzen.xlsx]D Finanzen'!$H$278:$H$301,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$A$278:$A$301,C10))</f>
-        <v/>
-      </c>
-      <c r="F10" s="6">
-        <f>IF(AND(C10&lt;='[Steuerung.xlsx]Steuerung'!$F$8,COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,4)&gt;0),'[GuV.xlsx]GuV'!I8,SUMIFS('[D Finanzen.xlsx]D Finanzen'!$F$278:$F$301,'[D Finanzen.xlsx]D Finanzen'!$H$278:$H$301,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$A$278:$A$301,C10))</f>
-        <v/>
-      </c>
-      <c r="G10" s="6">
-        <f>SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$506,'[FC Eingabe.xlsx]FC Eingabe'!$C$7:$C$506,'[Steuerung.xlsx]Steuerung'!$F$6,'[FC Eingabe.xlsx]FC Eingabe'!$D$7:$D$506,C10,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$506,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="H10" s="6">
-        <f>SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$506,'[FC Eingabe.xlsx]FC Eingabe'!$C$7:$C$506,'[Steuerung.xlsx]Steuerung'!$F$6,'[FC Eingabe.xlsx]FC Eingabe'!$D$7:$D$506,C10,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$506,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="I10" s="6">
-        <f>SUM(E10:H10)</f>
-        <v/>
-      </c>
-      <c r="J10" s="6">
-        <f>IF(AND(C10&lt;='[Steuerung.xlsx]Steuerung'!$F$8,COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,4)&gt;0),'[GuV.xlsx]GuV'!I20,SUMIFS('[D Finanzen.xlsx]D Finanzen'!$G$22:$G$33,'[D Finanzen.xlsx]D Finanzen'!$A$22:$A$33,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$22:$B$33,C10))</f>
-        <v/>
-      </c>
-      <c r="K10" s="6">
-        <f>SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$506,'[FC Eingabe.xlsx]FC Eingabe'!$C$7:$C$506,'[Steuerung.xlsx]Steuerung'!$F$6,'[FC Eingabe.xlsx]FC Eingabe'!$D$7:$D$506,C10,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$506,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="L10" s="6">
-        <f>J10+G10+H10-K10</f>
-        <v/>
-      </c>
-      <c r="M10" s="6">
-        <f>SUMIFS('[D Finanzen.xlsx]D Finanzen'!$D$182:$D$193,'[D Finanzen.xlsx]D Finanzen'!$A$182:$A$193,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$182:$B$193,C10)</f>
-        <v/>
-      </c>
-      <c r="N10" s="6">
-        <f>SUMIFS('[D Finanzen.xlsx]D Finanzen'!$G$182:$G$193,'[D Finanzen.xlsx]D Finanzen'!$A$182:$A$193,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$182:$B$193,C10)</f>
-        <v/>
-      </c>
-      <c r="O10" s="6">
-        <f>L10-N10</f>
-        <v/>
-      </c>
-      <c r="P10" s="7">
-        <f>IF(I10=0,"n.a.",L10/I10)</f>
-        <v/>
+      <c r="D10" s="1" t="inlineStr">
+        <is>
+          <t>IST</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>678343.59</v>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>1261219.89</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>1939563.48</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>-179274.07</v>
+      </c>
+      <c r="K10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" s="6" t="n">
+        <v>-179274.07</v>
+      </c>
+      <c r="M10" s="6" t="n">
+        <v>1348000</v>
+      </c>
+      <c r="N10" s="6" t="n">
+        <v>24000</v>
+      </c>
+      <c r="O10" s="6" t="n">
+        <v>-203274.07</v>
+      </c>
+      <c r="P10" s="7" t="n">
+        <v>-0.0924301121611137</v>
       </c>
       <c r="Q10" s="1" t="n"/>
     </row>
@@ -961,57 +917,46 @@
       <c r="C11" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="D11" s="1">
-        <f>IF(C11&lt;='[Steuerung.xlsx]Steuerung'!$F$8,"IST","FC")</f>
-        <v/>
-      </c>
-      <c r="E11" s="6">
-        <f>IF(AND(C11&lt;='[Steuerung.xlsx]Steuerung'!$F$8,COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,5)&gt;0),'[GuV.xlsx]GuV'!J7,SUMIFS('[D Finanzen.xlsx]D Finanzen'!$E$278:$E$301,'[D Finanzen.xlsx]D Finanzen'!$H$278:$H$301,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$A$278:$A$301,C11))</f>
-        <v/>
-      </c>
-      <c r="F11" s="6">
-        <f>IF(AND(C11&lt;='[Steuerung.xlsx]Steuerung'!$F$8,COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,5)&gt;0),'[GuV.xlsx]GuV'!J8,SUMIFS('[D Finanzen.xlsx]D Finanzen'!$F$278:$F$301,'[D Finanzen.xlsx]D Finanzen'!$H$278:$H$301,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$A$278:$A$301,C11))</f>
-        <v/>
-      </c>
-      <c r="G11" s="6">
-        <f>SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$506,'[FC Eingabe.xlsx]FC Eingabe'!$C$7:$C$506,'[Steuerung.xlsx]Steuerung'!$F$6,'[FC Eingabe.xlsx]FC Eingabe'!$D$7:$D$506,C11,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$506,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="H11" s="6">
-        <f>SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$506,'[FC Eingabe.xlsx]FC Eingabe'!$C$7:$C$506,'[Steuerung.xlsx]Steuerung'!$F$6,'[FC Eingabe.xlsx]FC Eingabe'!$D$7:$D$506,C11,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$506,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="I11" s="6">
-        <f>SUM(E11:H11)</f>
-        <v/>
-      </c>
-      <c r="J11" s="6">
-        <f>IF(AND(C11&lt;='[Steuerung.xlsx]Steuerung'!$F$8,COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,5)&gt;0),'[GuV.xlsx]GuV'!J20,SUMIFS('[D Finanzen.xlsx]D Finanzen'!$G$22:$G$33,'[D Finanzen.xlsx]D Finanzen'!$A$22:$A$33,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$22:$B$33,C11))</f>
-        <v/>
-      </c>
-      <c r="K11" s="6">
-        <f>SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$506,'[FC Eingabe.xlsx]FC Eingabe'!$C$7:$C$506,'[Steuerung.xlsx]Steuerung'!$F$6,'[FC Eingabe.xlsx]FC Eingabe'!$D$7:$D$506,C11,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$506,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="L11" s="6">
-        <f>J11+G11+H11-K11</f>
-        <v/>
-      </c>
-      <c r="M11" s="6">
-        <f>SUMIFS('[D Finanzen.xlsx]D Finanzen'!$D$182:$D$193,'[D Finanzen.xlsx]D Finanzen'!$A$182:$A$193,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$182:$B$193,C11)</f>
-        <v/>
-      </c>
-      <c r="N11" s="6">
-        <f>SUMIFS('[D Finanzen.xlsx]D Finanzen'!$G$182:$G$193,'[D Finanzen.xlsx]D Finanzen'!$A$182:$A$193,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$182:$B$193,C11)</f>
-        <v/>
-      </c>
-      <c r="O11" s="6">
-        <f>L11-N11</f>
-        <v/>
-      </c>
-      <c r="P11" s="7">
-        <f>IF(I11=0,"n.a.",L11/I11)</f>
-        <v/>
+      <c r="D11" s="1" t="inlineStr">
+        <is>
+          <t>IST</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>1347585.48</v>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>-263604.09</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>1083981.39</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>-141241.9</v>
+      </c>
+      <c r="K11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" s="6" t="n">
+        <v>-141241.9</v>
+      </c>
+      <c r="M11" s="6" t="n">
+        <v>1213000</v>
+      </c>
+      <c r="N11" s="6" t="n">
+        <v>-79000</v>
+      </c>
+      <c r="O11" s="6" t="n">
+        <v>-62241.89999999999</v>
+      </c>
+      <c r="P11" s="7" t="n">
+        <v>-0.1302991926826345</v>
       </c>
       <c r="Q11" s="1" t="n"/>
     </row>
@@ -1021,57 +966,46 @@
       <c r="C12" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="D12" s="1">
-        <f>IF(C12&lt;='[Steuerung.xlsx]Steuerung'!$F$8,"IST","FC")</f>
-        <v/>
-      </c>
-      <c r="E12" s="6">
-        <f>IF(AND(C12&lt;='[Steuerung.xlsx]Steuerung'!$F$8,COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,6)&gt;0),'[GuV.xlsx]GuV'!K7,SUMIFS('[D Finanzen.xlsx]D Finanzen'!$E$278:$E$301,'[D Finanzen.xlsx]D Finanzen'!$H$278:$H$301,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$A$278:$A$301,C12))</f>
-        <v/>
-      </c>
-      <c r="F12" s="6">
-        <f>IF(AND(C12&lt;='[Steuerung.xlsx]Steuerung'!$F$8,COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,6)&gt;0),'[GuV.xlsx]GuV'!K8,SUMIFS('[D Finanzen.xlsx]D Finanzen'!$F$278:$F$301,'[D Finanzen.xlsx]D Finanzen'!$H$278:$H$301,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$A$278:$A$301,C12))</f>
-        <v/>
-      </c>
-      <c r="G12" s="6">
-        <f>SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$506,'[FC Eingabe.xlsx]FC Eingabe'!$C$7:$C$506,'[Steuerung.xlsx]Steuerung'!$F$6,'[FC Eingabe.xlsx]FC Eingabe'!$D$7:$D$506,C12,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$506,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="H12" s="6">
-        <f>SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$506,'[FC Eingabe.xlsx]FC Eingabe'!$C$7:$C$506,'[Steuerung.xlsx]Steuerung'!$F$6,'[FC Eingabe.xlsx]FC Eingabe'!$D$7:$D$506,C12,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$506,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="I12" s="6">
-        <f>SUM(E12:H12)</f>
-        <v/>
-      </c>
-      <c r="J12" s="6">
-        <f>IF(AND(C12&lt;='[Steuerung.xlsx]Steuerung'!$F$8,COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,6)&gt;0),'[GuV.xlsx]GuV'!K20,SUMIFS('[D Finanzen.xlsx]D Finanzen'!$G$22:$G$33,'[D Finanzen.xlsx]D Finanzen'!$A$22:$A$33,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$22:$B$33,C12))</f>
-        <v/>
-      </c>
-      <c r="K12" s="6">
-        <f>SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$506,'[FC Eingabe.xlsx]FC Eingabe'!$C$7:$C$506,'[Steuerung.xlsx]Steuerung'!$F$6,'[FC Eingabe.xlsx]FC Eingabe'!$D$7:$D$506,C12,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$506,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="L12" s="6">
-        <f>J12+G12+H12-K12</f>
-        <v/>
-      </c>
-      <c r="M12" s="6">
-        <f>SUMIFS('[D Finanzen.xlsx]D Finanzen'!$D$182:$D$193,'[D Finanzen.xlsx]D Finanzen'!$A$182:$A$193,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$182:$B$193,C12)</f>
-        <v/>
-      </c>
-      <c r="N12" s="6">
-        <f>SUMIFS('[D Finanzen.xlsx]D Finanzen'!$G$182:$G$193,'[D Finanzen.xlsx]D Finanzen'!$A$182:$A$193,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$182:$B$193,C12)</f>
-        <v/>
-      </c>
-      <c r="O12" s="6">
-        <f>L12-N12</f>
-        <v/>
-      </c>
-      <c r="P12" s="7">
-        <f>IF(I12=0,"n.a.",L12/I12)</f>
-        <v/>
+      <c r="D12" s="1" t="inlineStr">
+        <is>
+          <t>IST</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>2470042.1</v>
+      </c>
+      <c r="F12" s="6" t="n">
+        <v>314645.23</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>2784687.33</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>58553.86</v>
+      </c>
+      <c r="K12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="6" t="n">
+        <v>58553.86</v>
+      </c>
+      <c r="M12" s="6" t="n">
+        <v>1483000</v>
+      </c>
+      <c r="N12" s="6" t="n">
+        <v>126000</v>
+      </c>
+      <c r="O12" s="6" t="n">
+        <v>-67446.14</v>
+      </c>
+      <c r="P12" s="7" t="n">
+        <v>0.02102708601040678</v>
       </c>
       <c r="Q12" s="1" t="n"/>
     </row>
@@ -1081,57 +1015,46 @@
       <c r="C13" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="D13" s="1">
-        <f>IF(C13&lt;='[Steuerung.xlsx]Steuerung'!$F$8,"IST","FC")</f>
-        <v/>
-      </c>
-      <c r="E13" s="6">
-        <f>IF(AND(C13&lt;='[Steuerung.xlsx]Steuerung'!$F$8,COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,7)&gt;0),'[GuV.xlsx]GuV'!L7,SUMIFS('[D Finanzen.xlsx]D Finanzen'!$E$278:$E$301,'[D Finanzen.xlsx]D Finanzen'!$H$278:$H$301,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$A$278:$A$301,C13))</f>
-        <v/>
-      </c>
-      <c r="F13" s="6">
-        <f>IF(AND(C13&lt;='[Steuerung.xlsx]Steuerung'!$F$8,COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,7)&gt;0),'[GuV.xlsx]GuV'!L8,SUMIFS('[D Finanzen.xlsx]D Finanzen'!$F$278:$F$301,'[D Finanzen.xlsx]D Finanzen'!$H$278:$H$301,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$A$278:$A$301,C13))</f>
-        <v/>
-      </c>
-      <c r="G13" s="6">
-        <f>SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$506,'[FC Eingabe.xlsx]FC Eingabe'!$C$7:$C$506,'[Steuerung.xlsx]Steuerung'!$F$6,'[FC Eingabe.xlsx]FC Eingabe'!$D$7:$D$506,C13,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$506,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="H13" s="6">
-        <f>SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$506,'[FC Eingabe.xlsx]FC Eingabe'!$C$7:$C$506,'[Steuerung.xlsx]Steuerung'!$F$6,'[FC Eingabe.xlsx]FC Eingabe'!$D$7:$D$506,C13,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$506,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="I13" s="6">
-        <f>SUM(E13:H13)</f>
-        <v/>
-      </c>
-      <c r="J13" s="6">
-        <f>IF(AND(C13&lt;='[Steuerung.xlsx]Steuerung'!$F$8,COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,7)&gt;0),'[GuV.xlsx]GuV'!L20,SUMIFS('[D Finanzen.xlsx]D Finanzen'!$G$22:$G$33,'[D Finanzen.xlsx]D Finanzen'!$A$22:$A$33,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$22:$B$33,C13))</f>
-        <v/>
-      </c>
-      <c r="K13" s="6">
-        <f>SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$506,'[FC Eingabe.xlsx]FC Eingabe'!$C$7:$C$506,'[Steuerung.xlsx]Steuerung'!$F$6,'[FC Eingabe.xlsx]FC Eingabe'!$D$7:$D$506,C13,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$506,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="L13" s="6">
-        <f>J13+G13+H13-K13</f>
-        <v/>
-      </c>
-      <c r="M13" s="6">
-        <f>SUMIFS('[D Finanzen.xlsx]D Finanzen'!$D$182:$D$193,'[D Finanzen.xlsx]D Finanzen'!$A$182:$A$193,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$182:$B$193,C13)</f>
-        <v/>
-      </c>
-      <c r="N13" s="6">
-        <f>SUMIFS('[D Finanzen.xlsx]D Finanzen'!$G$182:$G$193,'[D Finanzen.xlsx]D Finanzen'!$A$182:$A$193,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$182:$B$193,C13)</f>
-        <v/>
-      </c>
-      <c r="O13" s="6">
-        <f>L13-N13</f>
-        <v/>
-      </c>
-      <c r="P13" s="7">
-        <f>IF(I13=0,"n.a.",L13/I13)</f>
-        <v/>
+      <c r="D13" s="1" t="inlineStr">
+        <is>
+          <t>IST</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>1323928.2</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>294716.46</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>1618644.66</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>-495291.54</v>
+      </c>
+      <c r="K13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="6" t="n">
+        <v>-495291.54</v>
+      </c>
+      <c r="M13" s="6" t="n">
+        <v>1551000</v>
+      </c>
+      <c r="N13" s="6" t="n">
+        <v>178000</v>
+      </c>
+      <c r="O13" s="6" t="n">
+        <v>-673291.54</v>
+      </c>
+      <c r="P13" s="7" t="n">
+        <v>-0.3059915200906418</v>
       </c>
       <c r="Q13" s="1" t="n"/>
     </row>
@@ -1141,57 +1064,46 @@
       <c r="C14" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="D14" s="1">
-        <f>IF(C14&lt;='[Steuerung.xlsx]Steuerung'!$F$8,"IST","FC")</f>
-        <v/>
-      </c>
-      <c r="E14" s="6">
-        <f>IF(AND(C14&lt;='[Steuerung.xlsx]Steuerung'!$F$8,COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,8)&gt;0),'[GuV.xlsx]GuV'!M7,SUMIFS('[D Finanzen.xlsx]D Finanzen'!$E$278:$E$301,'[D Finanzen.xlsx]D Finanzen'!$H$278:$H$301,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$A$278:$A$301,C14))</f>
-        <v/>
-      </c>
-      <c r="F14" s="6">
-        <f>IF(AND(C14&lt;='[Steuerung.xlsx]Steuerung'!$F$8,COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,8)&gt;0),'[GuV.xlsx]GuV'!M8,SUMIFS('[D Finanzen.xlsx]D Finanzen'!$F$278:$F$301,'[D Finanzen.xlsx]D Finanzen'!$H$278:$H$301,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$A$278:$A$301,C14))</f>
-        <v/>
-      </c>
-      <c r="G14" s="6">
-        <f>SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$506,'[FC Eingabe.xlsx]FC Eingabe'!$C$7:$C$506,'[Steuerung.xlsx]Steuerung'!$F$6,'[FC Eingabe.xlsx]FC Eingabe'!$D$7:$D$506,C14,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$506,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="H14" s="6">
-        <f>SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$506,'[FC Eingabe.xlsx]FC Eingabe'!$C$7:$C$506,'[Steuerung.xlsx]Steuerung'!$F$6,'[FC Eingabe.xlsx]FC Eingabe'!$D$7:$D$506,C14,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$506,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="I14" s="6">
-        <f>SUM(E14:H14)</f>
-        <v/>
-      </c>
-      <c r="J14" s="6">
-        <f>IF(AND(C14&lt;='[Steuerung.xlsx]Steuerung'!$F$8,COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,8)&gt;0),'[GuV.xlsx]GuV'!M20,SUMIFS('[D Finanzen.xlsx]D Finanzen'!$G$22:$G$33,'[D Finanzen.xlsx]D Finanzen'!$A$22:$A$33,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$22:$B$33,C14))</f>
-        <v/>
-      </c>
-      <c r="K14" s="6">
-        <f>SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$506,'[FC Eingabe.xlsx]FC Eingabe'!$C$7:$C$506,'[Steuerung.xlsx]Steuerung'!$F$6,'[FC Eingabe.xlsx]FC Eingabe'!$D$7:$D$506,C14,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$506,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="L14" s="6">
-        <f>J14+G14+H14-K14</f>
-        <v/>
-      </c>
-      <c r="M14" s="6">
-        <f>SUMIFS('[D Finanzen.xlsx]D Finanzen'!$D$182:$D$193,'[D Finanzen.xlsx]D Finanzen'!$A$182:$A$193,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$182:$B$193,C14)</f>
-        <v/>
-      </c>
-      <c r="N14" s="6">
-        <f>SUMIFS('[D Finanzen.xlsx]D Finanzen'!$G$182:$G$193,'[D Finanzen.xlsx]D Finanzen'!$A$182:$A$193,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$182:$B$193,C14)</f>
-        <v/>
-      </c>
-      <c r="O14" s="6">
-        <f>L14-N14</f>
-        <v/>
-      </c>
-      <c r="P14" s="7">
-        <f>IF(I14=0,"n.a.",L14/I14)</f>
-        <v/>
+      <c r="D14" s="1" t="inlineStr">
+        <is>
+          <t>IST</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>854339.84</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>1022525.14</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>1876864.98</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-138242.37</v>
+      </c>
+      <c r="K14" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" s="6" t="n">
+        <v>-138242.37</v>
+      </c>
+      <c r="M14" s="6" t="n">
+        <v>1416000</v>
+      </c>
+      <c r="N14" s="6" t="n">
+        <v>76000</v>
+      </c>
+      <c r="O14" s="6" t="n">
+        <v>-214242.37</v>
+      </c>
+      <c r="P14" s="7" t="n">
+        <v>-0.07365600161605658</v>
       </c>
       <c r="Q14" s="1" t="n"/>
     </row>
@@ -1201,57 +1113,46 @@
       <c r="C15" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="D15" s="1">
-        <f>IF(C15&lt;='[Steuerung.xlsx]Steuerung'!$F$8,"IST","FC")</f>
-        <v/>
-      </c>
-      <c r="E15" s="6">
-        <f>IF(AND(C15&lt;='[Steuerung.xlsx]Steuerung'!$F$8,COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,9)&gt;0),'[GuV.xlsx]GuV'!N7,SUMIFS('[D Finanzen.xlsx]D Finanzen'!$E$278:$E$301,'[D Finanzen.xlsx]D Finanzen'!$H$278:$H$301,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$A$278:$A$301,C15))</f>
-        <v/>
-      </c>
-      <c r="F15" s="6">
-        <f>IF(AND(C15&lt;='[Steuerung.xlsx]Steuerung'!$F$8,COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,9)&gt;0),'[GuV.xlsx]GuV'!N8,SUMIFS('[D Finanzen.xlsx]D Finanzen'!$F$278:$F$301,'[D Finanzen.xlsx]D Finanzen'!$H$278:$H$301,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$A$278:$A$301,C15))</f>
-        <v/>
-      </c>
-      <c r="G15" s="6">
-        <f>SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$506,'[FC Eingabe.xlsx]FC Eingabe'!$C$7:$C$506,'[Steuerung.xlsx]Steuerung'!$F$6,'[FC Eingabe.xlsx]FC Eingabe'!$D$7:$D$506,C15,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$506,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="H15" s="6">
-        <f>SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$506,'[FC Eingabe.xlsx]FC Eingabe'!$C$7:$C$506,'[Steuerung.xlsx]Steuerung'!$F$6,'[FC Eingabe.xlsx]FC Eingabe'!$D$7:$D$506,C15,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$506,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="I15" s="6">
-        <f>SUM(E15:H15)</f>
-        <v/>
-      </c>
-      <c r="J15" s="6">
-        <f>IF(AND(C15&lt;='[Steuerung.xlsx]Steuerung'!$F$8,COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,9)&gt;0),'[GuV.xlsx]GuV'!N20,SUMIFS('[D Finanzen.xlsx]D Finanzen'!$G$22:$G$33,'[D Finanzen.xlsx]D Finanzen'!$A$22:$A$33,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$22:$B$33,C15))</f>
-        <v/>
-      </c>
-      <c r="K15" s="6">
-        <f>SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$506,'[FC Eingabe.xlsx]FC Eingabe'!$C$7:$C$506,'[Steuerung.xlsx]Steuerung'!$F$6,'[FC Eingabe.xlsx]FC Eingabe'!$D$7:$D$506,C15,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$506,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="L15" s="6">
-        <f>J15+G15+H15-K15</f>
-        <v/>
-      </c>
-      <c r="M15" s="6">
-        <f>SUMIFS('[D Finanzen.xlsx]D Finanzen'!$D$182:$D$193,'[D Finanzen.xlsx]D Finanzen'!$A$182:$A$193,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$182:$B$193,C15)</f>
-        <v/>
-      </c>
-      <c r="N15" s="6">
-        <f>SUMIFS('[D Finanzen.xlsx]D Finanzen'!$G$182:$G$193,'[D Finanzen.xlsx]D Finanzen'!$A$182:$A$193,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$182:$B$193,C15)</f>
-        <v/>
-      </c>
-      <c r="O15" s="6">
-        <f>L15-N15</f>
-        <v/>
-      </c>
-      <c r="P15" s="7">
-        <f>IF(I15=0,"n.a.",L15/I15)</f>
-        <v/>
+      <c r="D15" s="1" t="inlineStr">
+        <is>
+          <t>FC</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>2604944</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>2604944</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>309886</v>
+      </c>
+      <c r="K15" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" s="6" t="n">
+        <v>309886</v>
+      </c>
+      <c r="M15" s="6" t="n">
+        <v>1483000</v>
+      </c>
+      <c r="N15" s="6" t="n">
+        <v>125000</v>
+      </c>
+      <c r="O15" s="6" t="n">
+        <v>184886</v>
+      </c>
+      <c r="P15" s="7" t="n">
+        <v>0.1189607147025042</v>
       </c>
       <c r="Q15" s="1" t="n"/>
     </row>
@@ -1261,57 +1162,46 @@
       <c r="C16" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="D16" s="1">
-        <f>IF(C16&lt;='[Steuerung.xlsx]Steuerung'!$F$8,"IST","FC")</f>
-        <v/>
-      </c>
-      <c r="E16" s="6">
-        <f>IF(AND(C16&lt;='[Steuerung.xlsx]Steuerung'!$F$8,COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,10)&gt;0),'[GuV.xlsx]GuV'!O7,SUMIFS('[D Finanzen.xlsx]D Finanzen'!$E$278:$E$301,'[D Finanzen.xlsx]D Finanzen'!$H$278:$H$301,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$A$278:$A$301,C16))</f>
-        <v/>
-      </c>
-      <c r="F16" s="6">
-        <f>IF(AND(C16&lt;='[Steuerung.xlsx]Steuerung'!$F$8,COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,10)&gt;0),'[GuV.xlsx]GuV'!O8,SUMIFS('[D Finanzen.xlsx]D Finanzen'!$F$278:$F$301,'[D Finanzen.xlsx]D Finanzen'!$H$278:$H$301,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$A$278:$A$301,C16))</f>
-        <v/>
-      </c>
-      <c r="G16" s="6">
-        <f>SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$506,'[FC Eingabe.xlsx]FC Eingabe'!$C$7:$C$506,'[Steuerung.xlsx]Steuerung'!$F$6,'[FC Eingabe.xlsx]FC Eingabe'!$D$7:$D$506,C16,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$506,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="H16" s="6">
-        <f>SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$506,'[FC Eingabe.xlsx]FC Eingabe'!$C$7:$C$506,'[Steuerung.xlsx]Steuerung'!$F$6,'[FC Eingabe.xlsx]FC Eingabe'!$D$7:$D$506,C16,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$506,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="I16" s="6">
-        <f>SUM(E16:H16)</f>
-        <v/>
-      </c>
-      <c r="J16" s="6">
-        <f>IF(AND(C16&lt;='[Steuerung.xlsx]Steuerung'!$F$8,COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,10)&gt;0),'[GuV.xlsx]GuV'!O20,SUMIFS('[D Finanzen.xlsx]D Finanzen'!$G$22:$G$33,'[D Finanzen.xlsx]D Finanzen'!$A$22:$A$33,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$22:$B$33,C16))</f>
-        <v/>
-      </c>
-      <c r="K16" s="6">
-        <f>SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$506,'[FC Eingabe.xlsx]FC Eingabe'!$C$7:$C$506,'[Steuerung.xlsx]Steuerung'!$F$6,'[FC Eingabe.xlsx]FC Eingabe'!$D$7:$D$506,C16,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$506,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="L16" s="6">
-        <f>J16+G16+H16-K16</f>
-        <v/>
-      </c>
-      <c r="M16" s="6">
-        <f>SUMIFS('[D Finanzen.xlsx]D Finanzen'!$D$182:$D$193,'[D Finanzen.xlsx]D Finanzen'!$A$182:$A$193,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$182:$B$193,C16)</f>
-        <v/>
-      </c>
-      <c r="N16" s="6">
-        <f>SUMIFS('[D Finanzen.xlsx]D Finanzen'!$G$182:$G$193,'[D Finanzen.xlsx]D Finanzen'!$A$182:$A$193,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$182:$B$193,C16)</f>
-        <v/>
-      </c>
-      <c r="O16" s="6">
-        <f>L16-N16</f>
-        <v/>
-      </c>
-      <c r="P16" s="7">
-        <f>IF(I16=0,"n.a.",L16/I16)</f>
-        <v/>
+      <c r="D16" s="1" t="inlineStr">
+        <is>
+          <t>FC</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>1333000</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>1333000</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>118692</v>
+      </c>
+      <c r="K16" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" s="6" t="n">
+        <v>118692</v>
+      </c>
+      <c r="M16" s="6" t="n">
+        <v>1483000</v>
+      </c>
+      <c r="N16" s="6" t="n">
+        <v>125000</v>
+      </c>
+      <c r="O16" s="6" t="n">
+        <v>-6308</v>
+      </c>
+      <c r="P16" s="7" t="n">
+        <v>0.08904126031507877</v>
       </c>
       <c r="Q16" s="1" t="n"/>
     </row>
@@ -1321,57 +1211,46 @@
       <c r="C17" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="D17" s="1">
-        <f>IF(C17&lt;='[Steuerung.xlsx]Steuerung'!$F$8,"IST","FC")</f>
-        <v/>
-      </c>
-      <c r="E17" s="6">
-        <f>IF(AND(C17&lt;='[Steuerung.xlsx]Steuerung'!$F$8,COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,11)&gt;0),'[GuV.xlsx]GuV'!P7,SUMIFS('[D Finanzen.xlsx]D Finanzen'!$E$278:$E$301,'[D Finanzen.xlsx]D Finanzen'!$H$278:$H$301,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$A$278:$A$301,C17))</f>
-        <v/>
-      </c>
-      <c r="F17" s="6">
-        <f>IF(AND(C17&lt;='[Steuerung.xlsx]Steuerung'!$F$8,COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,11)&gt;0),'[GuV.xlsx]GuV'!P8,SUMIFS('[D Finanzen.xlsx]D Finanzen'!$F$278:$F$301,'[D Finanzen.xlsx]D Finanzen'!$H$278:$H$301,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$A$278:$A$301,C17))</f>
-        <v/>
-      </c>
-      <c r="G17" s="6">
-        <f>SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$506,'[FC Eingabe.xlsx]FC Eingabe'!$C$7:$C$506,'[Steuerung.xlsx]Steuerung'!$F$6,'[FC Eingabe.xlsx]FC Eingabe'!$D$7:$D$506,C17,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$506,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="H17" s="6">
-        <f>SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$506,'[FC Eingabe.xlsx]FC Eingabe'!$C$7:$C$506,'[Steuerung.xlsx]Steuerung'!$F$6,'[FC Eingabe.xlsx]FC Eingabe'!$D$7:$D$506,C17,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$506,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="I17" s="6">
-        <f>SUM(E17:H17)</f>
-        <v/>
-      </c>
-      <c r="J17" s="6">
-        <f>IF(AND(C17&lt;='[Steuerung.xlsx]Steuerung'!$F$8,COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,11)&gt;0),'[GuV.xlsx]GuV'!P20,SUMIFS('[D Finanzen.xlsx]D Finanzen'!$G$22:$G$33,'[D Finanzen.xlsx]D Finanzen'!$A$22:$A$33,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$22:$B$33,C17))</f>
-        <v/>
-      </c>
-      <c r="K17" s="6">
-        <f>SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$506,'[FC Eingabe.xlsx]FC Eingabe'!$C$7:$C$506,'[Steuerung.xlsx]Steuerung'!$F$6,'[FC Eingabe.xlsx]FC Eingabe'!$D$7:$D$506,C17,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$506,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="L17" s="6">
-        <f>J17+G17+H17-K17</f>
-        <v/>
-      </c>
-      <c r="M17" s="6">
-        <f>SUMIFS('[D Finanzen.xlsx]D Finanzen'!$D$182:$D$193,'[D Finanzen.xlsx]D Finanzen'!$A$182:$A$193,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$182:$B$193,C17)</f>
-        <v/>
-      </c>
-      <c r="N17" s="6">
-        <f>SUMIFS('[D Finanzen.xlsx]D Finanzen'!$G$182:$G$193,'[D Finanzen.xlsx]D Finanzen'!$A$182:$A$193,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$182:$B$193,C17)</f>
-        <v/>
-      </c>
-      <c r="O17" s="6">
-        <f>L17-N17</f>
-        <v/>
-      </c>
-      <c r="P17" s="7">
-        <f>IF(I17=0,"n.a.",L17/I17)</f>
-        <v/>
+      <c r="D17" s="1" t="inlineStr">
+        <is>
+          <t>FC</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>1775000</v>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>1775000</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>380092</v>
+      </c>
+      <c r="K17" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" s="6" t="n">
+        <v>380092</v>
+      </c>
+      <c r="M17" s="6" t="n">
+        <v>1416000</v>
+      </c>
+      <c r="N17" s="6" t="n">
+        <v>73000</v>
+      </c>
+      <c r="O17" s="6" t="n">
+        <v>307092</v>
+      </c>
+      <c r="P17" s="7" t="n">
+        <v>0.214136338028169</v>
       </c>
       <c r="Q17" s="1" t="n"/>
     </row>
@@ -1381,57 +1260,46 @@
       <c r="C18" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="D18" s="1">
-        <f>IF(C18&lt;='[Steuerung.xlsx]Steuerung'!$F$8,"IST","FC")</f>
-        <v/>
-      </c>
-      <c r="E18" s="6">
-        <f>IF(AND(C18&lt;='[Steuerung.xlsx]Steuerung'!$F$8,COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,12)&gt;0),'[GuV.xlsx]GuV'!Q7,SUMIFS('[D Finanzen.xlsx]D Finanzen'!$E$278:$E$301,'[D Finanzen.xlsx]D Finanzen'!$H$278:$H$301,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$A$278:$A$301,C18))</f>
-        <v/>
-      </c>
-      <c r="F18" s="6">
-        <f>IF(AND(C18&lt;='[Steuerung.xlsx]Steuerung'!$F$8,COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,12)&gt;0),'[GuV.xlsx]GuV'!Q8,SUMIFS('[D Finanzen.xlsx]D Finanzen'!$F$278:$F$301,'[D Finanzen.xlsx]D Finanzen'!$H$278:$H$301,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$A$278:$A$301,C18))</f>
-        <v/>
-      </c>
-      <c r="G18" s="6">
-        <f>SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$506,'[FC Eingabe.xlsx]FC Eingabe'!$C$7:$C$506,'[Steuerung.xlsx]Steuerung'!$F$6,'[FC Eingabe.xlsx]FC Eingabe'!$D$7:$D$506,C18,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$506,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="H18" s="6">
-        <f>SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$506,'[FC Eingabe.xlsx]FC Eingabe'!$C$7:$C$506,'[Steuerung.xlsx]Steuerung'!$F$6,'[FC Eingabe.xlsx]FC Eingabe'!$D$7:$D$506,C18,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$506,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="I18" s="6">
-        <f>SUM(E18:H18)</f>
-        <v/>
-      </c>
-      <c r="J18" s="6">
-        <f>IF(AND(C18&lt;='[Steuerung.xlsx]Steuerung'!$F$8,COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,12)&gt;0),'[GuV.xlsx]GuV'!Q20,SUMIFS('[D Finanzen.xlsx]D Finanzen'!$G$22:$G$33,'[D Finanzen.xlsx]D Finanzen'!$A$22:$A$33,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$22:$B$33,C18))</f>
-        <v/>
-      </c>
-      <c r="K18" s="6">
-        <f>SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$506,'[FC Eingabe.xlsx]FC Eingabe'!$C$7:$C$506,'[Steuerung.xlsx]Steuerung'!$F$6,'[FC Eingabe.xlsx]FC Eingabe'!$D$7:$D$506,C18,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$506,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="L18" s="6">
-        <f>J18+G18+H18-K18</f>
-        <v/>
-      </c>
-      <c r="M18" s="6">
-        <f>SUMIFS('[D Finanzen.xlsx]D Finanzen'!$D$182:$D$193,'[D Finanzen.xlsx]D Finanzen'!$A$182:$A$193,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$182:$B$193,C18)</f>
-        <v/>
-      </c>
-      <c r="N18" s="6">
-        <f>SUMIFS('[D Finanzen.xlsx]D Finanzen'!$G$182:$G$193,'[D Finanzen.xlsx]D Finanzen'!$A$182:$A$193,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$182:$B$193,C18)</f>
-        <v/>
-      </c>
-      <c r="O18" s="6">
-        <f>L18-N18</f>
-        <v/>
-      </c>
-      <c r="P18" s="7">
-        <f>IF(I18=0,"n.a.",L18/I18)</f>
-        <v/>
+      <c r="D18" s="1" t="inlineStr">
+        <is>
+          <t>FC</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>1073000</v>
+      </c>
+      <c r="F18" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>1073000</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>-110405</v>
+      </c>
+      <c r="K18" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" s="6" t="n">
+        <v>-110405</v>
+      </c>
+      <c r="M18" s="6" t="n">
+        <v>1483000</v>
+      </c>
+      <c r="N18" s="6" t="n">
+        <v>124000</v>
+      </c>
+      <c r="O18" s="6" t="n">
+        <v>-234405</v>
+      </c>
+      <c r="P18" s="7" t="n">
+        <v>-0.1028937558247903</v>
       </c>
       <c r="Q18" s="1" t="n"/>
     </row>
@@ -1463,53 +1331,41 @@
         </is>
       </c>
       <c r="D20" s="8" t="n"/>
-      <c r="E20" s="9">
-        <f>SUM(E7:E18)</f>
-        <v/>
-      </c>
-      <c r="F20" s="9">
-        <f>SUM(F7:F18)</f>
-        <v/>
-      </c>
-      <c r="G20" s="9">
-        <f>SUM(G7:G18)</f>
-        <v/>
-      </c>
-      <c r="H20" s="9">
-        <f>SUM(H7:H18)</f>
-        <v/>
-      </c>
-      <c r="I20" s="9">
-        <f>SUM(I7:I18)</f>
-        <v/>
-      </c>
-      <c r="J20" s="9">
-        <f>SUM(J7:J18)</f>
-        <v/>
-      </c>
-      <c r="K20" s="9">
-        <f>SUM(K7:K18)</f>
-        <v/>
-      </c>
-      <c r="L20" s="9">
-        <f>SUM(L7:L18)</f>
-        <v/>
-      </c>
-      <c r="M20" s="9">
-        <f>SUM(M7:M18)</f>
-        <v/>
-      </c>
-      <c r="N20" s="9">
-        <f>SUM(N7:N18)</f>
-        <v/>
-      </c>
-      <c r="O20" s="9">
-        <f>SUM(O7:O18)</f>
-        <v/>
-      </c>
-      <c r="P20" s="10">
-        <f>IF(I20=0,"n.a.",L20/I20)</f>
-        <v/>
+      <c r="E20" s="9" t="n">
+        <v>18090534.69</v>
+      </c>
+      <c r="F20" s="9" t="n">
+        <v>4908844.46</v>
+      </c>
+      <c r="G20" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="9" t="n">
+        <v>22999379.15</v>
+      </c>
+      <c r="J20" s="9" t="n">
+        <v>439877.29</v>
+      </c>
+      <c r="K20" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" s="9" t="n">
+        <v>439877.29</v>
+      </c>
+      <c r="M20" s="9" t="n">
+        <v>17123000</v>
+      </c>
+      <c r="N20" s="9" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="O20" s="9" t="n">
+        <v>-560122.7100000001</v>
+      </c>
+      <c r="P20" s="10" t="n">
+        <v>0.01912561583211259</v>
       </c>
       <c r="Q20" s="1" t="n"/>
     </row>
@@ -1548,9 +1404,8 @@
       <c r="I22" s="1" t="n"/>
       <c r="J22" s="1" t="n"/>
       <c r="K22" s="1" t="n"/>
-      <c r="L22" s="1">
-        <f>'[D Finanzen.xlsx]D Finanzen'!F39</f>
-        <v/>
+      <c r="L22" s="1" t="n">
+        <v>0</v>
       </c>
       <c r="M22" s="1" t="n"/>
       <c r="N22" s="1" t="n"/>
@@ -1574,9 +1429,8 @@
       <c r="I23" s="8" t="n"/>
       <c r="J23" s="8" t="n"/>
       <c r="K23" s="8" t="n"/>
-      <c r="L23" s="8">
-        <f>L20+L22</f>
-        <v/>
+      <c r="L23" s="8" t="n">
+        <v>439877.29</v>
       </c>
       <c r="M23" s="8" t="n"/>
       <c r="N23" s="8" t="n"/>
@@ -2137,21 +1991,17 @@
       <c r="K49" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="L49" s="6">
-        <f>F49+I49+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C49,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M49" s="6">
-        <f>G49+J49-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C49,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N49" s="6">
-        <f>H49+K49+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C49,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O49" s="6">
-        <f>SUM(L49:N49)</f>
-        <v/>
+      <c r="L49" s="6" t="n">
+        <v>24855.15</v>
+      </c>
+      <c r="M49" s="6" t="n">
+        <v>-13515.52</v>
+      </c>
+      <c r="N49" s="6" t="n">
+        <v>-10000</v>
+      </c>
+      <c r="O49" s="6" t="n">
+        <v>1339.630000000001</v>
       </c>
       <c r="P49" s="1" t="n"/>
       <c r="Q49" s="1" t="n"/>
@@ -2192,21 +2042,17 @@
       <c r="K50" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="L50" s="6">
-        <f>F50+I50+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C50,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M50" s="6">
-        <f>G50+J50-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C50,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N50" s="6">
-        <f>H50+K50+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C50,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O50" s="6">
-        <f>SUM(L50:N50)</f>
-        <v/>
+      <c r="L50" s="6" t="n">
+        <v>45582.42</v>
+      </c>
+      <c r="M50" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N50" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O50" s="6" t="n">
+        <v>45582.42</v>
       </c>
       <c r="P50" s="1" t="n"/>
       <c r="Q50" s="1" t="n"/>
@@ -2247,21 +2093,17 @@
       <c r="K51" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="L51" s="6">
-        <f>F51+I51+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C51,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M51" s="6">
-        <f>G51+J51-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C51,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N51" s="6">
-        <f>H51+K51+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C51,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O51" s="6">
-        <f>SUM(L51:N51)</f>
-        <v/>
+      <c r="L51" s="6" t="n">
+        <v>414976.03</v>
+      </c>
+      <c r="M51" s="6" t="n">
+        <v>-100883.26</v>
+      </c>
+      <c r="N51" s="6" t="n">
+        <v>-279004.22</v>
+      </c>
+      <c r="O51" s="6" t="n">
+        <v>35088.55000000005</v>
       </c>
       <c r="P51" s="1" t="n"/>
       <c r="Q51" s="1" t="n"/>
@@ -2302,21 +2144,17 @@
       <c r="K52" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="L52" s="6">
-        <f>F52+I52+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C52,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M52" s="6">
-        <f>G52+J52-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C52,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N52" s="6">
-        <f>H52+K52+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C52,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O52" s="6">
-        <f>SUM(L52:N52)</f>
-        <v/>
+      <c r="L52" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M52" s="6" t="n">
+        <v>-1084.64</v>
+      </c>
+      <c r="N52" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O52" s="6" t="n">
+        <v>-1084.64</v>
       </c>
       <c r="P52" s="1" t="n"/>
       <c r="Q52" s="1" t="n"/>
@@ -2357,21 +2195,17 @@
       <c r="K53" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="L53" s="6">
-        <f>F53+I53+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C53,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M53" s="6">
-        <f>G53+J53-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C53,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N53" s="6">
-        <f>H53+K53+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C53,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O53" s="6">
-        <f>SUM(L53:N53)</f>
-        <v/>
+      <c r="L53" s="6" t="n">
+        <v>442000</v>
+      </c>
+      <c r="M53" s="6" t="n">
+        <v>-349975.8</v>
+      </c>
+      <c r="N53" s="6" t="n">
+        <v>59.31</v>
+      </c>
+      <c r="O53" s="6" t="n">
+        <v>92083.51000000001</v>
       </c>
       <c r="P53" s="1" t="n"/>
       <c r="Q53" s="1" t="n"/>
@@ -2412,21 +2246,17 @@
       <c r="K54" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="L54" s="6">
-        <f>F54+I54+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C54,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M54" s="6">
-        <f>G54+J54-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C54,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N54" s="6">
-        <f>H54+K54+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C54,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O54" s="6">
-        <f>SUM(L54:N54)</f>
-        <v/>
+      <c r="L54" s="6" t="n">
+        <v>19000</v>
+      </c>
+      <c r="M54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N54" s="6" t="n">
+        <v>-24683.12</v>
+      </c>
+      <c r="O54" s="6" t="n">
+        <v>-5683.119999999999</v>
       </c>
       <c r="P54" s="1" t="n"/>
       <c r="Q54" s="1" t="n"/>
@@ -2467,21 +2297,17 @@
       <c r="K55" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="L55" s="6">
-        <f>F55+I55+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C55,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M55" s="6">
-        <f>G55+J55-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C55,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N55" s="6">
-        <f>H55+K55+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C55,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O55" s="6">
-        <f>SUM(L55:N55)</f>
-        <v/>
+      <c r="L55" s="6" t="n">
+        <v>49999</v>
+      </c>
+      <c r="M55" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N55" s="6" t="n">
+        <v>-44762.43</v>
+      </c>
+      <c r="O55" s="6" t="n">
+        <v>5236.57</v>
       </c>
       <c r="P55" s="1" t="n"/>
       <c r="Q55" s="1" t="n"/>
@@ -2522,21 +2348,17 @@
       <c r="K56" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="L56" s="6">
-        <f>F56+I56+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C56,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M56" s="6">
-        <f>G56+J56-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C56,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N56" s="6">
-        <f>H56+K56+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C56,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O56" s="6">
-        <f>SUM(L56:N56)</f>
-        <v/>
+      <c r="L56" s="6" t="n">
+        <v>37284</v>
+      </c>
+      <c r="M56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O56" s="6" t="n">
+        <v>37284</v>
       </c>
       <c r="P56" s="1" t="n"/>
       <c r="Q56" s="1" t="n"/>
@@ -2577,21 +2399,17 @@
       <c r="K57" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="L57" s="6">
-        <f>F57+I57+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C57,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M57" s="6">
-        <f>G57+J57-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C57,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N57" s="6">
-        <f>H57+K57+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C57,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O57" s="6">
-        <f>SUM(L57:N57)</f>
-        <v/>
+      <c r="L57" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M57" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N57" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O57" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="P57" s="1" t="n"/>
       <c r="Q57" s="1" t="n"/>
@@ -2632,21 +2450,17 @@
       <c r="K58" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="L58" s="6">
-        <f>F58+I58+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C58,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M58" s="6">
-        <f>G58+J58-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C58,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N58" s="6">
-        <f>H58+K58+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C58,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O58" s="6">
-        <f>SUM(L58:N58)</f>
-        <v/>
+      <c r="L58" s="6" t="n">
+        <v>48086.9</v>
+      </c>
+      <c r="M58" s="6" t="n">
+        <v>-31274.13</v>
+      </c>
+      <c r="N58" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O58" s="6" t="n">
+        <v>16812.77</v>
       </c>
       <c r="P58" s="1" t="n"/>
       <c r="Q58" s="1" t="n"/>
@@ -2687,21 +2501,17 @@
       <c r="K59" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="L59" s="6">
-        <f>F59+I59+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C59,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M59" s="6">
-        <f>G59+J59-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C59,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N59" s="6">
-        <f>H59+K59+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C59,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O59" s="6">
-        <f>SUM(L59:N59)</f>
-        <v/>
+      <c r="L59" s="6" t="n">
+        <v>21000</v>
+      </c>
+      <c r="M59" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N59" s="6" t="n">
+        <v>-13730.16</v>
+      </c>
+      <c r="O59" s="6" t="n">
+        <v>7269.84</v>
       </c>
       <c r="P59" s="1" t="n"/>
       <c r="Q59" s="1" t="n"/>
@@ -2742,21 +2552,17 @@
       <c r="K60" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="L60" s="6">
-        <f>F60+I60+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C60,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M60" s="6">
-        <f>G60+J60-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C60,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N60" s="6">
-        <f>H60+K60+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C60,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O60" s="6">
-        <f>SUM(L60:N60)</f>
-        <v/>
+      <c r="L60" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M60" s="6" t="n">
+        <v>-189.05</v>
+      </c>
+      <c r="N60" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O60" s="6" t="n">
+        <v>-189.05</v>
       </c>
       <c r="P60" s="1" t="n"/>
       <c r="Q60" s="1" t="n"/>
@@ -2795,21 +2601,17 @@
       <c r="K61" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L61" s="13">
-        <f>F61+I61+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C61,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M61" s="13">
-        <f>G61+J61-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C61,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N61" s="13">
-        <f>H61+K61+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C61,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O61" s="13">
-        <f>SUM(L61:N61)</f>
-        <v/>
+      <c r="L61" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M61" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N61" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O61" s="13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="62" ht="21" customHeight="1">
@@ -2846,21 +2648,17 @@
       <c r="K62" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L62" s="13">
-        <f>F62+I62+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C62,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M62" s="13">
-        <f>G62+J62-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C62,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N62" s="13">
-        <f>H62+K62+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C62,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O62" s="13">
-        <f>SUM(L62:N62)</f>
-        <v/>
+      <c r="L62" s="13" t="n">
+        <v>827176.51</v>
+      </c>
+      <c r="M62" s="13" t="n">
+        <v>-137348.38</v>
+      </c>
+      <c r="N62" s="13" t="n">
+        <v>-578657.23</v>
+      </c>
+      <c r="O62" s="13" t="n">
+        <v>111170.9</v>
       </c>
     </row>
     <row r="63" ht="21" customHeight="1">
@@ -2897,21 +2695,17 @@
       <c r="K63" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L63" s="13">
-        <f>F63+I63+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C63,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M63" s="13">
-        <f>G63+J63-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C63,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N63" s="13">
-        <f>H63+K63+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C63,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O63" s="13">
-        <f>SUM(L63:N63)</f>
-        <v/>
+      <c r="L63" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M63" s="13" t="n">
+        <v>-6.1</v>
+      </c>
+      <c r="N63" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O63" s="13" t="n">
+        <v>-6.1</v>
       </c>
     </row>
     <row r="64" ht="21" customHeight="1">
@@ -2948,21 +2742,17 @@
       <c r="K64" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L64" s="13">
-        <f>F64+I64+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C64,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M64" s="13">
-        <f>G64+J64-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C64,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N64" s="13">
-        <f>H64+K64+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C64,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O64" s="13">
-        <f>SUM(L64:N64)</f>
-        <v/>
+      <c r="L64" s="13" t="n">
+        <v>40150.9</v>
+      </c>
+      <c r="M64" s="13" t="n">
+        <v>-1893113.68</v>
+      </c>
+      <c r="N64" s="13" t="n">
+        <v>2134210.44</v>
+      </c>
+      <c r="O64" s="13" t="n">
+        <v>281247.6599999999</v>
       </c>
     </row>
     <row r="65" ht="21" customHeight="1">
@@ -2999,21 +2789,17 @@
       <c r="K65" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L65" s="13">
-        <f>F65+I65+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C65,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M65" s="13">
-        <f>G65+J65-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C65,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N65" s="13">
-        <f>H65+K65+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C65,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O65" s="13">
-        <f>SUM(L65:N65)</f>
-        <v/>
+      <c r="L65" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M65" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N65" s="13" t="n">
+        <v>-2847.73</v>
+      </c>
+      <c r="O65" s="13" t="n">
+        <v>-2847.73</v>
       </c>
     </row>
     <row r="66" ht="21" customHeight="1">
@@ -3050,21 +2836,17 @@
       <c r="K66" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L66" s="13">
-        <f>F66+I66+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C66,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M66" s="13">
-        <f>G66+J66-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C66,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N66" s="13">
-        <f>H66+K66+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C66,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O66" s="13">
-        <f>SUM(L66:N66)</f>
-        <v/>
+      <c r="L66" s="13" t="n">
+        <v>1176663.57</v>
+      </c>
+      <c r="M66" s="13" t="n">
+        <v>-699485.9</v>
+      </c>
+      <c r="N66" s="13" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="O66" s="13" t="n">
+        <v>477177.66</v>
       </c>
     </row>
     <row r="67" ht="21" customHeight="1">
@@ -3101,21 +2883,17 @@
       <c r="K67" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L67" s="13">
-        <f>F67+I67+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C67,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M67" s="13">
-        <f>G67+J67-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C67,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N67" s="13">
-        <f>H67+K67+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C67,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O67" s="13">
-        <f>SUM(L67:N67)</f>
-        <v/>
+      <c r="L67" s="13" t="n">
+        <v>2223000</v>
+      </c>
+      <c r="M67" s="13" t="n">
+        <v>-5369042.73</v>
+      </c>
+      <c r="N67" s="13" t="n">
+        <v>3166169.81</v>
+      </c>
+      <c r="O67" s="13" t="n">
+        <v>20127.07999999961</v>
       </c>
     </row>
     <row r="68" ht="21" customHeight="1">
@@ -3152,21 +2930,17 @@
       <c r="K68" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L68" s="13">
-        <f>F68+I68+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C68,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M68" s="13">
-        <f>G68+J68-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C68,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N68" s="13">
-        <f>H68+K68+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C68,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O68" s="13">
-        <f>SUM(L68:N68)</f>
-        <v/>
+      <c r="L68" s="13" t="n">
+        <v>103280</v>
+      </c>
+      <c r="M68" s="13" t="n">
+        <v>-69993.84</v>
+      </c>
+      <c r="N68" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O68" s="13" t="n">
+        <v>33286.16</v>
       </c>
     </row>
     <row r="69" ht="21" customHeight="1">
@@ -3203,21 +2977,17 @@
       <c r="K69" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L69" s="13">
-        <f>F69+I69+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C69,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M69" s="13">
-        <f>G69+J69-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C69,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N69" s="13">
-        <f>H69+K69+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C69,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O69" s="13">
-        <f>SUM(L69:N69)</f>
-        <v/>
+      <c r="L69" s="13" t="n">
+        <v>407730.1</v>
+      </c>
+      <c r="M69" s="13" t="n">
+        <v>-226134.19</v>
+      </c>
+      <c r="N69" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O69" s="13" t="n">
+        <v>181595.91</v>
       </c>
     </row>
     <row r="70" ht="21" customHeight="1">
@@ -3254,21 +3024,17 @@
       <c r="K70" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L70" s="13">
-        <f>F70+I70+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C70,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M70" s="13">
-        <f>G70+J70-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C70,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N70" s="13">
-        <f>H70+K70+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C70,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O70" s="13">
-        <f>SUM(L70:N70)</f>
-        <v/>
+      <c r="L70" s="13" t="n">
+        <v>27473.13</v>
+      </c>
+      <c r="M70" s="13" t="n">
+        <v>-4953.57</v>
+      </c>
+      <c r="N70" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O70" s="13" t="n">
+        <v>22519.56</v>
       </c>
     </row>
     <row r="71" ht="21" customHeight="1">
@@ -3305,21 +3071,17 @@
       <c r="K71" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L71" s="13">
-        <f>F71+I71+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C71,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M71" s="13">
-        <f>G71+J71-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C71,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N71" s="13">
-        <f>H71+K71+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C71,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O71" s="13">
-        <f>SUM(L71:N71)</f>
-        <v/>
+      <c r="L71" s="13" t="n">
+        <v>32538</v>
+      </c>
+      <c r="M71" s="13" t="n">
+        <v>-15918.45</v>
+      </c>
+      <c r="N71" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O71" s="13" t="n">
+        <v>16619.55</v>
       </c>
     </row>
     <row r="72" ht="21" customHeight="1">
@@ -3356,21 +3118,17 @@
       <c r="K72" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L72" s="13">
-        <f>F72+I72+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C72,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M72" s="13">
-        <f>G72+J72-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C72,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N72" s="13">
-        <f>H72+K72+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C72,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O72" s="13">
-        <f>SUM(L72:N72)</f>
-        <v/>
+      <c r="L72" s="13" t="n">
+        <v>37000</v>
+      </c>
+      <c r="M72" s="13" t="n">
+        <v>-22614.95</v>
+      </c>
+      <c r="N72" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O72" s="13" t="n">
+        <v>14385.05</v>
       </c>
     </row>
     <row r="73" ht="21" customHeight="1">
@@ -3407,21 +3165,17 @@
       <c r="K73" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L73" s="13">
-        <f>F73+I73+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C73,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M73" s="13">
-        <f>G73+J73-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C73,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N73" s="13">
-        <f>H73+K73+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C73,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O73" s="13">
-        <f>SUM(L73:N73)</f>
-        <v/>
+      <c r="L73" s="13" t="n">
+        <v>27918.14</v>
+      </c>
+      <c r="M73" s="13" t="n">
+        <v>-30897.53</v>
+      </c>
+      <c r="N73" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O73" s="13" t="n">
+        <v>-2979.389999999999</v>
       </c>
     </row>
     <row r="74" ht="21" customHeight="1">
@@ -3458,21 +3212,17 @@
       <c r="K74" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L74" s="13">
-        <f>F74+I74+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C74,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M74" s="13">
-        <f>G74+J74-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C74,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N74" s="13">
-        <f>H74+K74+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C74,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O74" s="13">
-        <f>SUM(L74:N74)</f>
-        <v/>
+      <c r="L74" s="13" t="n">
+        <v>1093987.57</v>
+      </c>
+      <c r="M74" s="13" t="n">
+        <v>-1226166.21</v>
+      </c>
+      <c r="N74" s="13" t="n">
+        <v>327267.27</v>
+      </c>
+      <c r="O74" s="13" t="n">
+        <v>195088.6299999999</v>
       </c>
     </row>
     <row r="75" ht="21" customHeight="1">
@@ -3509,21 +3259,17 @@
       <c r="K75" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L75" s="13">
-        <f>F75+I75+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C75,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M75" s="13">
-        <f>G75+J75-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C75,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N75" s="13">
-        <f>H75+K75+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C75,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O75" s="13">
-        <f>SUM(L75:N75)</f>
-        <v/>
+      <c r="L75" s="13" t="n">
+        <v>23745</v>
+      </c>
+      <c r="M75" s="13" t="n">
+        <v>-15967</v>
+      </c>
+      <c r="N75" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O75" s="13" t="n">
+        <v>7778</v>
       </c>
     </row>
     <row r="76" ht="21" customHeight="1">
@@ -3560,21 +3306,17 @@
       <c r="K76" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L76" s="13">
-        <f>F76+I76+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C76,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M76" s="13">
-        <f>G76+J76-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C76,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N76" s="13">
-        <f>H76+K76+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C76,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O76" s="13">
-        <f>SUM(L76:N76)</f>
-        <v/>
+      <c r="L76" s="13" t="n">
+        <v>16000</v>
+      </c>
+      <c r="M76" s="13" t="n">
+        <v>-8117.03</v>
+      </c>
+      <c r="N76" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O76" s="13" t="n">
+        <v>7882.97</v>
       </c>
     </row>
     <row r="77" ht="21" customHeight="1">
@@ -3611,21 +3353,17 @@
       <c r="K77" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L77" s="13">
-        <f>F77+I77+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C77,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M77" s="13">
-        <f>G77+J77-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C77,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N77" s="13">
-        <f>H77+K77+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C77,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O77" s="13">
-        <f>SUM(L77:N77)</f>
-        <v/>
+      <c r="L77" s="13" t="n">
+        <v>15250</v>
+      </c>
+      <c r="M77" s="13" t="n">
+        <v>-8192.09</v>
+      </c>
+      <c r="N77" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O77" s="13" t="n">
+        <v>7057.91</v>
       </c>
     </row>
     <row r="78" ht="21" customHeight="1">
@@ -3662,21 +3400,17 @@
       <c r="K78" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L78" s="13">
-        <f>F78+I78+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C78,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M78" s="13">
-        <f>G78+J78-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C78,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N78" s="13">
-        <f>H78+K78+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C78,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O78" s="13">
-        <f>SUM(L78:N78)</f>
-        <v/>
+      <c r="L78" s="13" t="n">
+        <v>450000</v>
+      </c>
+      <c r="M78" s="13" t="n">
+        <v>-224000</v>
+      </c>
+      <c r="N78" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O78" s="13" t="n">
+        <v>226000</v>
       </c>
     </row>
     <row r="79" ht="21" customHeight="1">
@@ -3713,21 +3447,17 @@
       <c r="K79" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L79" s="13">
-        <f>F79+I79+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C79,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M79" s="13">
-        <f>G79+J79-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C79,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N79" s="13">
-        <f>H79+K79+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C79,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O79" s="13">
-        <f>SUM(L79:N79)</f>
-        <v/>
+      <c r="L79" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M79" s="13" t="n">
+        <v>-31262.12</v>
+      </c>
+      <c r="N79" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O79" s="13" t="n">
+        <v>-31262.12</v>
       </c>
     </row>
     <row r="80" ht="21" customHeight="1">
@@ -3764,21 +3494,17 @@
       <c r="K80" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L80" s="13">
-        <f>F80+I80+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C80,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M80" s="13">
-        <f>G80+J80-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C80,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N80" s="13">
-        <f>H80+K80+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C80,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O80" s="13">
-        <f>SUM(L80:N80)</f>
-        <v/>
+      <c r="L80" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M80" s="13" t="n">
+        <v>-3228.29</v>
+      </c>
+      <c r="N80" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O80" s="13" t="n">
+        <v>-3228.29</v>
       </c>
     </row>
     <row r="81" ht="21" customHeight="1">
@@ -3815,21 +3541,17 @@
       <c r="K81" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L81" s="13">
-        <f>F81+I81+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C81,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M81" s="13">
-        <f>G81+J81-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C81,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N81" s="13">
-        <f>H81+K81+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C81,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O81" s="13">
-        <f>SUM(L81:N81)</f>
-        <v/>
+      <c r="L81" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M81" s="13" t="n">
+        <v>-1337.87</v>
+      </c>
+      <c r="N81" s="13" t="n">
+        <v>124.87</v>
+      </c>
+      <c r="O81" s="13" t="n">
+        <v>-1213</v>
       </c>
     </row>
     <row r="82" ht="21" customHeight="1">
@@ -3866,21 +3588,17 @@
       <c r="K82" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L82" s="13">
-        <f>F82+I82+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C82,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M82" s="13">
-        <f>G82+J82-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C82,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N82" s="13">
-        <f>H82+K82+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C82,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O82" s="13">
-        <f>SUM(L82:N82)</f>
-        <v/>
+      <c r="L82" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M82" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N82" s="13" t="n">
+        <v>-7000</v>
+      </c>
+      <c r="O82" s="13" t="n">
+        <v>-7000</v>
       </c>
     </row>
     <row r="83" ht="21" customHeight="1">
@@ -3917,21 +3635,17 @@
       <c r="K83" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L83" s="13">
-        <f>F83+I83+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C83,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M83" s="13">
-        <f>G83+J83-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C83,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N83" s="13">
-        <f>H83+K83+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C83,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O83" s="13">
-        <f>SUM(L83:N83)</f>
-        <v/>
+      <c r="L83" s="13" t="n">
+        <v>66000</v>
+      </c>
+      <c r="M83" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N83" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O83" s="13" t="n">
+        <v>66000</v>
       </c>
     </row>
     <row r="84" ht="21" customHeight="1">
@@ -3968,21 +3682,17 @@
       <c r="K84" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L84" s="13">
-        <f>F84+I84+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C84,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M84" s="13">
-        <f>G84+J84-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C84,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N84" s="13">
-        <f>H84+K84+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C84,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O84" s="13">
-        <f>SUM(L84:N84)</f>
-        <v/>
+      <c r="L84" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M84" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N84" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O84" s="13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="85" ht="21" customHeight="1">
@@ -4019,21 +3729,17 @@
       <c r="K85" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L85" s="13">
-        <f>F85+I85+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C85,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M85" s="13">
-        <f>G85+J85-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C85,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N85" s="13">
-        <f>H85+K85+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C85,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O85" s="13">
-        <f>SUM(L85:N85)</f>
-        <v/>
+      <c r="L85" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M85" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N85" s="13" t="n">
+        <v>-25780.46</v>
+      </c>
+      <c r="O85" s="13" t="n">
+        <v>-25780.46</v>
       </c>
     </row>
     <row r="86" ht="21" customHeight="1">
@@ -4070,21 +3776,17 @@
       <c r="K86" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L86" s="13">
-        <f>F86+I86+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C86,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M86" s="13">
-        <f>G86+J86-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C86,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N86" s="13">
-        <f>H86+K86+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C86,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O86" s="13">
-        <f>SUM(L86:N86)</f>
-        <v/>
+      <c r="L86" s="13" t="n">
+        <v>1613.33</v>
+      </c>
+      <c r="M86" s="13" t="n">
+        <v>-17995.46</v>
+      </c>
+      <c r="N86" s="13" t="n">
+        <v>-10353.48</v>
+      </c>
+      <c r="O86" s="13" t="n">
+        <v>-26735.61</v>
       </c>
     </row>
     <row r="87" ht="21" customHeight="1">
@@ -4121,21 +3823,17 @@
       <c r="K87" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L87" s="13">
-        <f>F87+I87+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C87,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M87" s="13">
-        <f>G87+J87-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C87,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N87" s="13">
-        <f>H87+K87+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C87,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O87" s="13">
-        <f>SUM(L87:N87)</f>
-        <v/>
+      <c r="L87" s="13" t="n">
+        <v>29755.02</v>
+      </c>
+      <c r="M87" s="13" t="n">
+        <v>-31000</v>
+      </c>
+      <c r="N87" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O87" s="13" t="n">
+        <v>-1244.98</v>
       </c>
     </row>
     <row r="88" ht="21" customHeight="1">
@@ -4172,21 +3870,17 @@
       <c r="K88" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L88" s="13">
-        <f>F88+I88+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C88,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M88" s="13">
-        <f>G88+J88-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C88,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N88" s="13">
-        <f>H88+K88+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C88,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O88" s="13">
-        <f>SUM(L88:N88)</f>
-        <v/>
+      <c r="L88" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M88" s="13" t="n">
+        <v>-166.84</v>
+      </c>
+      <c r="N88" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O88" s="13" t="n">
+        <v>-166.84</v>
       </c>
     </row>
     <row r="89" ht="21" customHeight="1">
@@ -4223,21 +3917,17 @@
       <c r="K89" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L89" s="13">
-        <f>F89+I89+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C89,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M89" s="13">
-        <f>G89+J89-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C89,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N89" s="13">
-        <f>H89+K89+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C89,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O89" s="13">
-        <f>SUM(L89:N89)</f>
-        <v/>
+      <c r="L89" s="13" t="n">
+        <v>50236.26</v>
+      </c>
+      <c r="M89" s="13" t="n">
+        <v>-31447.44</v>
+      </c>
+      <c r="N89" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O89" s="13" t="n">
+        <v>18788.82</v>
       </c>
     </row>
     <row r="90" ht="21" customHeight="1">
@@ -4274,21 +3964,17 @@
       <c r="K90" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L90" s="13">
-        <f>F90+I90+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C90,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M90" s="13">
-        <f>G90+J90-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C90,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N90" s="13">
-        <f>H90+K90+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C90,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O90" s="13">
-        <f>SUM(L90:N90)</f>
-        <v/>
+      <c r="L90" s="13" t="n">
+        <v>140570.44</v>
+      </c>
+      <c r="M90" s="13" t="n">
+        <v>-158381.2</v>
+      </c>
+      <c r="N90" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O90" s="13" t="n">
+        <v>-17810.76000000001</v>
       </c>
     </row>
     <row r="91" ht="21" customHeight="1">
@@ -4325,21 +4011,17 @@
       <c r="K91" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L91" s="13">
-        <f>F91+I91+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C91,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M91" s="13">
-        <f>G91+J91-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C91,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N91" s="13">
-        <f>H91+K91+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C91,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O91" s="13">
-        <f>SUM(L91:N91)</f>
-        <v/>
+      <c r="L91" s="13" t="n">
+        <v>198536.25</v>
+      </c>
+      <c r="M91" s="13" t="n">
+        <v>-36767.86</v>
+      </c>
+      <c r="N91" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O91" s="13" t="n">
+        <v>161768.39</v>
       </c>
     </row>
     <row r="92" ht="21" customHeight="1">
@@ -4376,21 +4058,17 @@
       <c r="K92" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L92" s="13">
-        <f>F92+I92+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C92,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M92" s="13">
-        <f>G92+J92-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C92,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N92" s="13">
-        <f>H92+K92+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C92,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O92" s="13">
-        <f>SUM(L92:N92)</f>
-        <v/>
+      <c r="L92" s="13" t="n">
+        <v>47313.87</v>
+      </c>
+      <c r="M92" s="13" t="n">
+        <v>-11295.81</v>
+      </c>
+      <c r="N92" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O92" s="13" t="n">
+        <v>36018.06</v>
       </c>
     </row>
     <row r="93" ht="21" customHeight="1">
@@ -4427,21 +4105,17 @@
       <c r="K93" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L93" s="13">
-        <f>F93+I93+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C93,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M93" s="13">
-        <f>G93+J93-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C93,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N93" s="13">
-        <f>H93+K93+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C93,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O93" s="13">
-        <f>SUM(L93:N93)</f>
-        <v/>
+      <c r="L93" s="13" t="n">
+        <v>42425.11</v>
+      </c>
+      <c r="M93" s="13" t="n">
+        <v>-19891.85</v>
+      </c>
+      <c r="N93" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O93" s="13" t="n">
+        <v>22533.26</v>
       </c>
     </row>
     <row r="94" ht="21" customHeight="1">
@@ -4478,21 +4152,17 @@
       <c r="K94" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L94" s="13">
-        <f>F94+I94+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C94,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M94" s="13">
-        <f>G94+J94-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C94,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N94" s="13">
-        <f>H94+K94+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C94,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O94" s="13">
-        <f>SUM(L94:N94)</f>
-        <v/>
+      <c r="L94" s="13" t="n">
+        <v>97490.11</v>
+      </c>
+      <c r="M94" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N94" s="13" t="n">
+        <v>-83199.77</v>
+      </c>
+      <c r="O94" s="13" t="n">
+        <v>14290.34</v>
       </c>
     </row>
     <row r="95" ht="21" customHeight="1">
@@ -4529,21 +4199,17 @@
       <c r="K95" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L95" s="13">
-        <f>F95+I95+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C95,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M95" s="13">
-        <f>G95+J95-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C95,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N95" s="13">
-        <f>H95+K95+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C95,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O95" s="13">
-        <f>SUM(L95:N95)</f>
-        <v/>
+      <c r="L95" s="13" t="n">
+        <v>85258.00999999999</v>
+      </c>
+      <c r="M95" s="13" t="n">
+        <v>-30600</v>
+      </c>
+      <c r="N95" s="13" t="n">
+        <v>-39732.85</v>
+      </c>
+      <c r="O95" s="13" t="n">
+        <v>14925.16</v>
       </c>
     </row>
     <row r="96" ht="21" customHeight="1">
@@ -4580,21 +4246,17 @@
       <c r="K96" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L96" s="13">
-        <f>F96+I96+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C96,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M96" s="13">
-        <f>G96+J96-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C96,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N96" s="13">
-        <f>H96+K96+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C96,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O96" s="13">
-        <f>SUM(L96:N96)</f>
-        <v/>
+      <c r="L96" s="13" t="n">
+        <v>1045320.52</v>
+      </c>
+      <c r="M96" s="13" t="n">
+        <v>-945817.55</v>
+      </c>
+      <c r="N96" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O96" s="13" t="n">
+        <v>99502.96999999997</v>
       </c>
     </row>
     <row r="97" ht="21" customHeight="1">
@@ -4631,21 +4293,17 @@
       <c r="K97" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L97" s="13">
-        <f>F97+I97+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C97,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M97" s="13">
-        <f>G97+J97-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C97,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N97" s="13">
-        <f>H97+K97+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C97,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O97" s="13">
-        <f>SUM(L97:N97)</f>
-        <v/>
+      <c r="L97" s="13" t="n">
+        <v>60554.04</v>
+      </c>
+      <c r="M97" s="13" t="n">
+        <v>-22058.42</v>
+      </c>
+      <c r="N97" s="13" t="n">
+        <v>-46621</v>
+      </c>
+      <c r="O97" s="13" t="n">
+        <v>-8125.379999999997</v>
       </c>
     </row>
     <row r="98" ht="21" customHeight="1">
@@ -4682,21 +4340,17 @@
       <c r="K98" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L98" s="13">
-        <f>F98+I98+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C98,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M98" s="13">
-        <f>G98+J98-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C98,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N98" s="13">
-        <f>H98+K98+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C98,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O98" s="13">
-        <f>SUM(L98:N98)</f>
-        <v/>
+      <c r="L98" s="13" t="n">
+        <v>240770.35</v>
+      </c>
+      <c r="M98" s="13" t="n">
+        <v>-142710.2</v>
+      </c>
+      <c r="N98" s="13" t="n">
+        <v>-168400.34</v>
+      </c>
+      <c r="O98" s="13" t="n">
+        <v>-70340.19</v>
       </c>
     </row>
     <row r="99" ht="21" customHeight="1">
@@ -4733,21 +4387,17 @@
       <c r="K99" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L99" s="13">
-        <f>F99+I99+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C99,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M99" s="13">
-        <f>G99+J99-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C99,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N99" s="13">
-        <f>H99+K99+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C99,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O99" s="13">
-        <f>SUM(L99:N99)</f>
-        <v/>
+      <c r="L99" s="13" t="n">
+        <v>51822.08</v>
+      </c>
+      <c r="M99" s="13" t="n">
+        <v>-56256.37</v>
+      </c>
+      <c r="N99" s="13" t="n">
+        <v>5723.3</v>
+      </c>
+      <c r="O99" s="13" t="n">
+        <v>1289.009999999999</v>
       </c>
     </row>
     <row r="100" ht="21" customHeight="1">
@@ -4784,21 +4434,17 @@
       <c r="K100" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L100" s="13">
-        <f>F100+I100+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C100,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M100" s="13">
-        <f>G100+J100-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C100,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N100" s="13">
-        <f>H100+K100+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C100,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O100" s="13">
-        <f>SUM(L100:N100)</f>
-        <v/>
+      <c r="L100" s="13" t="n">
+        <v>66801.86</v>
+      </c>
+      <c r="M100" s="13" t="n">
+        <v>-188.19</v>
+      </c>
+      <c r="N100" s="13" t="n">
+        <v>-66752</v>
+      </c>
+      <c r="O100" s="13" t="n">
+        <v>-138.3300000000017</v>
       </c>
     </row>
     <row r="101" ht="21" customHeight="1">
@@ -4835,21 +4481,17 @@
       <c r="K101" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L101" s="13">
-        <f>F101+I101+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C101,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M101" s="13">
-        <f>G101+J101-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C101,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N101" s="13">
-        <f>H101+K101+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C101,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O101" s="13">
-        <f>SUM(L101:N101)</f>
-        <v/>
+      <c r="L101" s="13" t="n">
+        <v>101108.3</v>
+      </c>
+      <c r="M101" s="13" t="n">
+        <v>-136207.51</v>
+      </c>
+      <c r="N101" s="13" t="n">
+        <v>66878.32000000001</v>
+      </c>
+      <c r="O101" s="13" t="n">
+        <v>31779.11</v>
       </c>
     </row>
     <row r="102" ht="21" customHeight="1">
@@ -4886,21 +4528,17 @@
       <c r="K102" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L102" s="13">
-        <f>F102+I102+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C102,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M102" s="13">
-        <f>G102+J102-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C102,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N102" s="13">
-        <f>H102+K102+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C102,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O102" s="13">
-        <f>SUM(L102:N102)</f>
-        <v/>
+      <c r="L102" s="13" t="n">
+        <v>167270.25</v>
+      </c>
+      <c r="M102" s="13" t="n">
+        <v>-154560.54</v>
+      </c>
+      <c r="N102" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O102" s="13" t="n">
+        <v>12709.71000000002</v>
       </c>
     </row>
     <row r="103" ht="21" customHeight="1">
@@ -4937,21 +4575,17 @@
       <c r="K103" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L103" s="13">
-        <f>F103+I103+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C103,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M103" s="13">
-        <f>G103+J103-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C103,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N103" s="13">
-        <f>H103+K103+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C103,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O103" s="13">
-        <f>SUM(L103:N103)</f>
-        <v/>
+      <c r="L103" s="13" t="n">
+        <v>249898.21</v>
+      </c>
+      <c r="M103" s="13" t="n">
+        <v>-161600.06</v>
+      </c>
+      <c r="N103" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O103" s="13" t="n">
+        <v>88298.14999999999</v>
       </c>
     </row>
     <row r="104" ht="21" customHeight="1">
@@ -4988,21 +4622,17 @@
       <c r="K104" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L104" s="13">
-        <f>F104+I104+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C104,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M104" s="13">
-        <f>G104+J104-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C104,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N104" s="13">
-        <f>H104+K104+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C104,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O104" s="13">
-        <f>SUM(L104:N104)</f>
-        <v/>
+      <c r="L104" s="13" t="n">
+        <v>50827.6</v>
+      </c>
+      <c r="M104" s="13" t="n">
+        <v>-16165.48</v>
+      </c>
+      <c r="N104" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O104" s="13" t="n">
+        <v>34662.12</v>
       </c>
     </row>
     <row r="105" ht="21" customHeight="1">
@@ -5039,21 +4669,17 @@
       <c r="K105" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L105" s="13">
-        <f>F105+I105+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C105,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M105" s="13">
-        <f>G105+J105-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C105,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N105" s="13">
-        <f>H105+K105+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C105,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O105" s="13">
-        <f>SUM(L105:N105)</f>
-        <v/>
+      <c r="L105" s="13" t="n">
+        <v>9232.4</v>
+      </c>
+      <c r="M105" s="13" t="n">
+        <v>-68659.09</v>
+      </c>
+      <c r="N105" s="13" t="n">
+        <v>77704.58</v>
+      </c>
+      <c r="O105" s="13" t="n">
+        <v>18277.89000000001</v>
       </c>
     </row>
     <row r="106" ht="21" customHeight="1">
@@ -5090,21 +4716,17 @@
       <c r="K106" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L106" s="13">
-        <f>F106+I106+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C106,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M106" s="13">
-        <f>G106+J106-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C106,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N106" s="13">
-        <f>H106+K106+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C106,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O106" s="13">
-        <f>SUM(L106:N106)</f>
-        <v/>
+      <c r="L106" s="13" t="n">
+        <v>314773.65</v>
+      </c>
+      <c r="M106" s="13" t="n">
+        <v>-326088.97</v>
+      </c>
+      <c r="N106" s="13" t="n">
+        <v>59730.99</v>
+      </c>
+      <c r="O106" s="13" t="n">
+        <v>48415.67000000005</v>
       </c>
     </row>
     <row r="107" ht="21" customHeight="1">
@@ -5141,21 +4763,17 @@
       <c r="K107" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L107" s="13">
-        <f>F107+I107+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C107,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M107" s="13">
-        <f>G107+J107-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C107,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N107" s="13">
-        <f>H107+K107+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C107,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O107" s="13">
-        <f>SUM(L107:N107)</f>
-        <v/>
+      <c r="L107" s="13" t="n">
+        <v>685850.0600000001</v>
+      </c>
+      <c r="M107" s="13" t="n">
+        <v>-777406.29</v>
+      </c>
+      <c r="N107" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O107" s="13" t="n">
+        <v>-91556.22999999998</v>
       </c>
     </row>
     <row r="108" ht="21" customHeight="1">
@@ -5192,21 +4810,17 @@
       <c r="K108" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L108" s="13">
-        <f>F108+I108+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C108,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M108" s="13">
-        <f>G108+J108-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C108,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N108" s="13">
-        <f>H108+K108+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C108,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O108" s="13">
-        <f>SUM(L108:N108)</f>
-        <v/>
+      <c r="L108" s="13" t="n">
+        <v>68000</v>
+      </c>
+      <c r="M108" s="13" t="n">
+        <v>-41600</v>
+      </c>
+      <c r="N108" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O108" s="13" t="n">
+        <v>26400</v>
       </c>
     </row>
     <row r="109" ht="21" customHeight="1">
@@ -5243,21 +4857,17 @@
       <c r="K109" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L109" s="13">
-        <f>F109+I109+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C109,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M109" s="13">
-        <f>G109+J109-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C109,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N109" s="13">
-        <f>H109+K109+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C109,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O109" s="13">
-        <f>SUM(L109:N109)</f>
-        <v/>
+      <c r="L109" s="13" t="n">
+        <v>45000</v>
+      </c>
+      <c r="M109" s="13" t="n">
+        <v>-34000</v>
+      </c>
+      <c r="N109" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O109" s="13" t="n">
+        <v>11000</v>
       </c>
     </row>
     <row r="110" ht="21" customHeight="1">
@@ -5294,21 +4904,17 @@
       <c r="K110" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L110" s="13">
-        <f>F110+I110+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C110,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M110" s="13">
-        <f>G110+J110-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C110,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N110" s="13">
-        <f>H110+K110+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C110,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O110" s="13">
-        <f>SUM(L110:N110)</f>
-        <v/>
+      <c r="L110" s="13" t="n">
+        <v>60444.44</v>
+      </c>
+      <c r="M110" s="13" t="n">
+        <v>-46837.81</v>
+      </c>
+      <c r="N110" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O110" s="13" t="n">
+        <v>13606.63</v>
       </c>
     </row>
     <row r="111" ht="21" customHeight="1">
@@ -5345,21 +4951,17 @@
       <c r="K111" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L111" s="13">
-        <f>F111+I111+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C111,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M111" s="13">
-        <f>G111+J111-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C111,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N111" s="13">
-        <f>H111+K111+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C111,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O111" s="13">
-        <f>SUM(L111:N111)</f>
-        <v/>
+      <c r="L111" s="13" t="n">
+        <v>99829.8</v>
+      </c>
+      <c r="M111" s="13" t="n">
+        <v>-93695.45999999999</v>
+      </c>
+      <c r="N111" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O111" s="13" t="n">
+        <v>6134.340000000011</v>
       </c>
     </row>
     <row r="112" ht="21" customHeight="1">
@@ -5396,21 +4998,17 @@
       <c r="K112" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L112" s="13">
-        <f>F112+I112+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C112,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M112" s="13">
-        <f>G112+J112-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C112,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N112" s="13">
-        <f>H112+K112+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C112,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O112" s="13">
-        <f>SUM(L112:N112)</f>
-        <v/>
+      <c r="L112" s="13" t="n">
+        <v>341996.66</v>
+      </c>
+      <c r="M112" s="13" t="n">
+        <v>-278919.52</v>
+      </c>
+      <c r="N112" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O112" s="13" t="n">
+        <v>63077.14000000001</v>
       </c>
     </row>
     <row r="113" ht="21" customHeight="1">
@@ -5447,21 +5045,17 @@
       <c r="K113" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L113" s="13">
-        <f>F113+I113+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C113,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M113" s="13">
-        <f>G113+J113-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C113,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N113" s="13">
-        <f>H113+K113+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C113,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O113" s="13">
-        <f>SUM(L113:N113)</f>
-        <v/>
+      <c r="L113" s="13" t="n">
+        <v>252500</v>
+      </c>
+      <c r="M113" s="13" t="n">
+        <v>-236621.75</v>
+      </c>
+      <c r="N113" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O113" s="13" t="n">
+        <v>15878.25</v>
       </c>
     </row>
     <row r="114" ht="21" customHeight="1">
@@ -5498,21 +5092,17 @@
       <c r="K114" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L114" s="13">
-        <f>F114+I114+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C114,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M114" s="13">
-        <f>G114+J114-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C114,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N114" s="13">
-        <f>H114+K114+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C114,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O114" s="13">
-        <f>SUM(L114:N114)</f>
-        <v/>
+      <c r="L114" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M114" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N114" s="13" t="n">
+        <v>-6447.83</v>
+      </c>
+      <c r="O114" s="13" t="n">
+        <v>-6447.83</v>
       </c>
     </row>
     <row r="115" ht="21" customHeight="1">
@@ -5549,21 +5139,17 @@
       <c r="K115" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L115" s="13">
-        <f>F115+I115+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C115,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M115" s="13">
-        <f>G115+J115-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C115,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N115" s="13">
-        <f>H115+K115+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C115,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O115" s="13">
-        <f>SUM(L115:N115)</f>
-        <v/>
+      <c r="L115" s="13" t="n">
+        <v>133273.51</v>
+      </c>
+      <c r="M115" s="13" t="n">
+        <v>-96408.7</v>
+      </c>
+      <c r="N115" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O115" s="13" t="n">
+        <v>36864.81000000001</v>
       </c>
     </row>
     <row r="116" ht="21" customHeight="1">
@@ -5600,21 +5186,17 @@
       <c r="K116" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L116" s="13">
-        <f>F116+I116+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C116,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M116" s="13">
-        <f>G116+J116-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C116,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N116" s="13">
-        <f>H116+K116+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C116,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O116" s="13">
-        <f>SUM(L116:N116)</f>
-        <v/>
+      <c r="L116" s="13" t="n">
+        <v>24410.59</v>
+      </c>
+      <c r="M116" s="13" t="n">
+        <v>-15778</v>
+      </c>
+      <c r="N116" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O116" s="13" t="n">
+        <v>8632.59</v>
       </c>
     </row>
     <row r="117" ht="21" customHeight="1">
@@ -5651,21 +5233,17 @@
       <c r="K117" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L117" s="13">
-        <f>F117+I117+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C117,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M117" s="13">
-        <f>G117+J117-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C117,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N117" s="13">
-        <f>H117+K117+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C117,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O117" s="13">
-        <f>SUM(L117:N117)</f>
-        <v/>
+      <c r="L117" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M117" s="13" t="n">
+        <v>-5293.57</v>
+      </c>
+      <c r="N117" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O117" s="13" t="n">
+        <v>-5293.57</v>
       </c>
     </row>
     <row r="118" ht="21" customHeight="1">
@@ -5702,21 +5280,17 @@
       <c r="K118" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L118" s="13">
-        <f>F118+I118+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C118,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M118" s="13">
-        <f>G118+J118-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C118,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N118" s="13">
-        <f>H118+K118+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C118,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O118" s="13">
-        <f>SUM(L118:N118)</f>
-        <v/>
+      <c r="L118" s="13" t="n">
+        <v>1055.73</v>
+      </c>
+      <c r="M118" s="13" t="n">
+        <v>-9771.620000000001</v>
+      </c>
+      <c r="N118" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O118" s="13" t="n">
+        <v>-8715.890000000001</v>
       </c>
     </row>
     <row r="119" ht="21" customHeight="1">
@@ -5753,21 +5327,17 @@
       <c r="K119" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L119" s="13">
-        <f>F119+I119+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C119,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M119" s="13">
-        <f>G119+J119-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C119,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N119" s="13">
-        <f>H119+K119+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C119,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O119" s="13">
-        <f>SUM(L119:N119)</f>
-        <v/>
+      <c r="L119" s="13" t="n">
+        <v>113903.69</v>
+      </c>
+      <c r="M119" s="13" t="n">
+        <v>-32842.94</v>
+      </c>
+      <c r="N119" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O119" s="13" t="n">
+        <v>81060.75</v>
       </c>
     </row>
     <row r="120" ht="21" customHeight="1">
@@ -5804,21 +5374,17 @@
       <c r="K120" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L120" s="13">
-        <f>F120+I120+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C120,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M120" s="13">
-        <f>G120+J120-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C120,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N120" s="13">
-        <f>H120+K120+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C120,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O120" s="13">
-        <f>SUM(L120:N120)</f>
-        <v/>
+      <c r="L120" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M120" s="13" t="n">
+        <v>-1758.75</v>
+      </c>
+      <c r="N120" s="13" t="n">
+        <v>1969.8</v>
+      </c>
+      <c r="O120" s="13" t="n">
+        <v>211.05</v>
       </c>
     </row>
     <row r="121" ht="21" customHeight="1">
@@ -5855,21 +5421,17 @@
       <c r="K121" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L121" s="13">
-        <f>F121+I121+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C121,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M121" s="13">
-        <f>G121+J121-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C121,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N121" s="13">
-        <f>H121+K121+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C121,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O121" s="13">
-        <f>SUM(L121:N121)</f>
-        <v/>
+      <c r="L121" s="13" t="n">
+        <v>57000</v>
+      </c>
+      <c r="M121" s="13" t="n">
+        <v>-45400.43</v>
+      </c>
+      <c r="N121" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O121" s="13" t="n">
+        <v>11599.57</v>
       </c>
     </row>
     <row r="122" ht="21" customHeight="1">
@@ -5906,21 +5468,17 @@
       <c r="K122" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L122" s="13">
-        <f>F122+I122+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C122,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M122" s="13">
-        <f>G122+J122-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C122,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N122" s="13">
-        <f>H122+K122+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C122,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O122" s="13">
-        <f>SUM(L122:N122)</f>
-        <v/>
+      <c r="L122" s="13" t="n">
+        <v>6059.53</v>
+      </c>
+      <c r="M122" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N122" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O122" s="13" t="n">
+        <v>6059.53</v>
       </c>
     </row>
     <row r="123" ht="21" customHeight="1">
@@ -5957,21 +5515,17 @@
       <c r="K123" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L123" s="13">
-        <f>F123+I123+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C123,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M123" s="13">
-        <f>G123+J123-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C123,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N123" s="13">
-        <f>H123+K123+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C123,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O123" s="13">
-        <f>SUM(L123:N123)</f>
-        <v/>
+      <c r="L123" s="13" t="n">
+        <v>831914.5700000001</v>
+      </c>
+      <c r="M123" s="13" t="n">
+        <v>-667333.29</v>
+      </c>
+      <c r="N123" s="13" t="n">
+        <v>854549.58</v>
+      </c>
+      <c r="O123" s="13" t="n">
+        <v>1019130.86</v>
       </c>
     </row>
     <row r="124" ht="21" customHeight="1">
@@ -6008,21 +5562,17 @@
       <c r="K124" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L124" s="13">
-        <f>F124+I124+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C124,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M124" s="13">
-        <f>G124+J124-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C124,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N124" s="13">
-        <f>H124+K124+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C124,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O124" s="13">
-        <f>SUM(L124:N124)</f>
-        <v/>
+      <c r="L124" s="13" t="n">
+        <v>125327.66</v>
+      </c>
+      <c r="M124" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N124" s="13" t="n">
+        <v>-44321.39</v>
+      </c>
+      <c r="O124" s="13" t="n">
+        <v>81006.27</v>
       </c>
     </row>
     <row r="125" ht="21" customHeight="1">
@@ -6059,21 +5609,17 @@
       <c r="K125" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L125" s="13">
-        <f>F125+I125+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C125,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M125" s="13">
-        <f>G125+J125-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C125,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N125" s="13">
-        <f>H125+K125+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C125,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O125" s="13">
-        <f>SUM(L125:N125)</f>
-        <v/>
+      <c r="L125" s="13" t="n">
+        <v>36649.67</v>
+      </c>
+      <c r="M125" s="13" t="n">
+        <v>-27469.51</v>
+      </c>
+      <c r="N125" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O125" s="13" t="n">
+        <v>9180.16</v>
       </c>
     </row>
     <row r="126" ht="21" customHeight="1">
@@ -6110,21 +5656,17 @@
       <c r="K126" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L126" s="13">
-        <f>F126+I126+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C126,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M126" s="13">
-        <f>G126+J126-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C126,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N126" s="13">
-        <f>H126+K126+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C126,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O126" s="13">
-        <f>SUM(L126:N126)</f>
-        <v/>
+      <c r="L126" s="13" t="n">
+        <v>4502058.58</v>
+      </c>
+      <c r="M126" s="13" t="n">
+        <v>-2735704.88</v>
+      </c>
+      <c r="N126" s="13" t="n">
+        <v>-870769.6</v>
+      </c>
+      <c r="O126" s="13" t="n">
+        <v>895584.1000000002</v>
       </c>
     </row>
     <row r="127" ht="21" customHeight="1">
@@ -6161,21 +5703,17 @@
       <c r="K127" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L127" s="13">
-        <f>F127+I127+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C127,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M127" s="13">
-        <f>G127+J127-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C127,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N127" s="13">
-        <f>H127+K127+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C127,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O127" s="13">
-        <f>SUM(L127:N127)</f>
-        <v/>
+      <c r="L127" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M127" s="13" t="n">
+        <v>-583.34</v>
+      </c>
+      <c r="N127" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O127" s="13" t="n">
+        <v>-583.34</v>
       </c>
     </row>
     <row r="128" ht="21" customHeight="1">
@@ -6212,21 +5750,17 @@
       <c r="K128" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L128" s="13">
-        <f>F128+I128+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C128,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M128" s="13">
-        <f>G128+J128-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C128,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N128" s="13">
-        <f>H128+K128+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C128,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O128" s="13">
-        <f>SUM(L128:N128)</f>
-        <v/>
+      <c r="L128" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M128" s="13" t="n">
+        <v>-3096.72</v>
+      </c>
+      <c r="N128" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O128" s="13" t="n">
+        <v>-3096.72</v>
       </c>
     </row>
     <row r="129" ht="21" customHeight="1">
@@ -6263,21 +5797,17 @@
       <c r="K129" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L129" s="13">
-        <f>F129+I129+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C129,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M129" s="13">
-        <f>G129+J129-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C129,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N129" s="13">
-        <f>H129+K129+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C129,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O129" s="13">
-        <f>SUM(L129:N129)</f>
-        <v/>
+      <c r="L129" s="13" t="n">
+        <v>-591.8099999999999</v>
+      </c>
+      <c r="M129" s="13" t="n">
+        <v>-279.03</v>
+      </c>
+      <c r="N129" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O129" s="13" t="n">
+        <v>-870.8399999999999</v>
       </c>
     </row>
     <row r="130" ht="21" customHeight="1">
@@ -6314,21 +5844,17 @@
       <c r="K130" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L130" s="13">
-        <f>F130+I130+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C130,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M130" s="13">
-        <f>G130+J130-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C130,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N130" s="13">
-        <f>H130+K130+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C130,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O130" s="13">
-        <f>SUM(L130:N130)</f>
-        <v/>
+      <c r="L130" s="13" t="n">
+        <v>28224.24</v>
+      </c>
+      <c r="M130" s="13" t="n">
+        <v>-20068.44</v>
+      </c>
+      <c r="N130" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O130" s="13" t="n">
+        <v>8155.800000000003</v>
       </c>
     </row>
     <row r="131" ht="21" customHeight="1">
@@ -6365,21 +5891,17 @@
       <c r="K131" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L131" s="13">
-        <f>F131+I131+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C131,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M131" s="13">
-        <f>G131+J131-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C131,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N131" s="13">
-        <f>H131+K131+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C131,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O131" s="13">
-        <f>SUM(L131:N131)</f>
-        <v/>
+      <c r="L131" s="13" t="n">
+        <v>5542.71</v>
+      </c>
+      <c r="M131" s="13" t="n">
+        <v>-556.45</v>
+      </c>
+      <c r="N131" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O131" s="13" t="n">
+        <v>4986.26</v>
       </c>
     </row>
     <row r="132" ht="21" customHeight="1">
@@ -6416,21 +5938,17 @@
       <c r="K132" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L132" s="13">
-        <f>F132+I132+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C132,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M132" s="13">
-        <f>G132+J132-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C132,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N132" s="13">
-        <f>H132+K132+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C132,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O132" s="13">
-        <f>SUM(L132:N132)</f>
-        <v/>
+      <c r="L132" s="13" t="n">
+        <v>130358.55</v>
+      </c>
+      <c r="M132" s="13" t="n">
+        <v>-30672.84</v>
+      </c>
+      <c r="N132" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O132" s="13" t="n">
+        <v>99685.71000000001</v>
       </c>
     </row>
     <row r="133" ht="21" customHeight="1">
@@ -6467,21 +5985,17 @@
       <c r="K133" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L133" s="13">
-        <f>F133+I133+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C133,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M133" s="13">
-        <f>G133+J133-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C133,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N133" s="13">
-        <f>H133+K133+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C133,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O133" s="13">
-        <f>SUM(L133:N133)</f>
-        <v/>
+      <c r="L133" s="13" t="n">
+        <v>203470.4</v>
+      </c>
+      <c r="M133" s="13" t="n">
+        <v>-23848.96</v>
+      </c>
+      <c r="N133" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O133" s="13" t="n">
+        <v>179621.44</v>
       </c>
     </row>
     <row r="134" ht="21" customHeight="1">
@@ -6518,21 +6032,17 @@
       <c r="K134" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L134" s="13">
-        <f>F134+I134+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C134,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M134" s="13">
-        <f>G134+J134-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C134,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N134" s="13">
-        <f>H134+K134+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C134,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O134" s="13">
-        <f>SUM(L134:N134)</f>
-        <v/>
+      <c r="L134" s="13" t="n">
+        <v>25652.08</v>
+      </c>
+      <c r="M134" s="13" t="n">
+        <v>-9699</v>
+      </c>
+      <c r="N134" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O134" s="13" t="n">
+        <v>15953.08</v>
       </c>
     </row>
     <row r="135" ht="21" customHeight="1">
@@ -6569,21 +6079,17 @@
       <c r="K135" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L135" s="13">
-        <f>F135+I135+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C135,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M135" s="13">
-        <f>G135+J135-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C135,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N135" s="13">
-        <f>H135+K135+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C135,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O135" s="13">
-        <f>SUM(L135:N135)</f>
-        <v/>
+      <c r="L135" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M135" s="13" t="n">
+        <v>-100</v>
+      </c>
+      <c r="N135" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O135" s="13" t="n">
+        <v>-100</v>
       </c>
     </row>
     <row r="136" ht="21" customHeight="1">
@@ -6620,21 +6126,17 @@
       <c r="K136" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L136" s="13">
-        <f>F136+I136+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C136,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M136" s="13">
-        <f>G136+J136-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C136,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N136" s="13">
-        <f>H136+K136+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C136,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O136" s="13">
-        <f>SUM(L136:N136)</f>
-        <v/>
+      <c r="L136" s="13" t="n">
+        <v>16500</v>
+      </c>
+      <c r="M136" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N136" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O136" s="13" t="n">
+        <v>16500</v>
       </c>
     </row>
     <row r="137" ht="21" customHeight="1">
@@ -6671,21 +6173,17 @@
       <c r="K137" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L137" s="13">
-        <f>F137+I137+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C137,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M137" s="13">
-        <f>G137+J137-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C137,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N137" s="13">
-        <f>H137+K137+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C137,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O137" s="13">
-        <f>SUM(L137:N137)</f>
-        <v/>
+      <c r="L137" s="13" t="n">
+        <v>-59785.46</v>
+      </c>
+      <c r="M137" s="13" t="n">
+        <v>-3.3</v>
+      </c>
+      <c r="N137" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O137" s="13" t="n">
+        <v>-59788.76</v>
       </c>
     </row>
     <row r="138" ht="21" customHeight="1">
@@ -6722,21 +6220,17 @@
       <c r="K138" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L138" s="13">
-        <f>F138+I138+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C138,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M138" s="13">
-        <f>G138+J138-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C138,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N138" s="13">
-        <f>H138+K138+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C138,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O138" s="13">
-        <f>SUM(L138:N138)</f>
-        <v/>
+      <c r="L138" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M138" s="13" t="n">
+        <v>-424.37</v>
+      </c>
+      <c r="N138" s="13" t="n">
+        <v>475.29</v>
+      </c>
+      <c r="O138" s="13" t="n">
+        <v>50.92000000000002</v>
       </c>
     </row>
     <row r="139" ht="21" customHeight="1">
@@ -6773,21 +6267,17 @@
       <c r="K139" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L139" s="13">
-        <f>F139+I139+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C139,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M139" s="13">
-        <f>G139+J139-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C139,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N139" s="13">
-        <f>H139+K139+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C139,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O139" s="13">
-        <f>SUM(L139:N139)</f>
-        <v/>
+      <c r="L139" s="13" t="n">
+        <v>9697.700000000001</v>
+      </c>
+      <c r="M139" s="13" t="n">
+        <v>-392074.26</v>
+      </c>
+      <c r="N139" s="13" t="n">
+        <v>406981.1</v>
+      </c>
+      <c r="O139" s="13" t="n">
+        <v>24604.53999999998</v>
       </c>
     </row>
     <row r="140" ht="21" customHeight="1">
@@ -6824,21 +6314,17 @@
       <c r="K140" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L140" s="13">
-        <f>F140+I140+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C140,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M140" s="13">
-        <f>G140+J140-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C140,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N140" s="13">
-        <f>H140+K140+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C140,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O140" s="13">
-        <f>SUM(L140:N140)</f>
-        <v/>
+      <c r="L140" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M140" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N140" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O140" s="13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="141" ht="21" customHeight="1">
@@ -6875,21 +6361,17 @@
       <c r="K141" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L141" s="13">
-        <f>F141+I141+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C141,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M141" s="13">
-        <f>G141+J141-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C141,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N141" s="13">
-        <f>H141+K141+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C141,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O141" s="13">
-        <f>SUM(L141:N141)</f>
-        <v/>
+      <c r="L141" s="13" t="n">
+        <v>-39809.7</v>
+      </c>
+      <c r="M141" s="13" t="n">
+        <v>8.970000000000001</v>
+      </c>
+      <c r="N141" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O141" s="13" t="n">
+        <v>-39800.73</v>
       </c>
     </row>
     <row r="142" ht="21" customHeight="1">
@@ -6926,21 +6408,17 @@
       <c r="K142" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L142" s="13">
-        <f>F142+I142+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C142,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M142" s="13">
-        <f>G142+J142-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C142,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N142" s="13">
-        <f>H142+K142+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C142,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O142" s="13">
-        <f>SUM(L142:N142)</f>
-        <v/>
+      <c r="L142" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M142" s="13" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="N142" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O142" s="13" t="n">
+        <v>0.15</v>
       </c>
     </row>
     <row r="143" ht="21" customHeight="1">
@@ -6977,21 +6455,17 @@
       <c r="K143" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L143" s="13">
-        <f>F143+I143+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C143,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M143" s="13">
-        <f>G143+J143-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C143,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N143" s="13">
-        <f>H143+K143+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C143,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O143" s="13">
-        <f>SUM(L143:N143)</f>
-        <v/>
+      <c r="L143" s="13" t="n">
+        <v>302672.02</v>
+      </c>
+      <c r="M143" s="13" t="n">
+        <v>-59955.88</v>
+      </c>
+      <c r="N143" s="13" t="n">
+        <v>-70767.05</v>
+      </c>
+      <c r="O143" s="13" t="n">
+        <v>171949.09</v>
       </c>
     </row>
     <row r="144" ht="21" customHeight="1">
@@ -7028,21 +6502,17 @@
       <c r="K144" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L144" s="13">
-        <f>F144+I144+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C144,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M144" s="13">
-        <f>G144+J144-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C144,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N144" s="13">
-        <f>H144+K144+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C144,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O144" s="13">
-        <f>SUM(L144:N144)</f>
-        <v/>
+      <c r="L144" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M144" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N144" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O144" s="13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="145" ht="21" customHeight="1">
@@ -7079,21 +6549,17 @@
       <c r="K145" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L145" s="13">
-        <f>F145+I145+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C145,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M145" s="13">
-        <f>G145+J145-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C145,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N145" s="13">
-        <f>H145+K145+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C145,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O145" s="13">
-        <f>SUM(L145:N145)</f>
-        <v/>
+      <c r="L145" s="13" t="n">
+        <v>59491.68</v>
+      </c>
+      <c r="M145" s="13" t="n">
+        <v>-67801.53999999999</v>
+      </c>
+      <c r="N145" s="13" t="n">
+        <v>117116.98</v>
+      </c>
+      <c r="O145" s="13" t="n">
+        <v>108807.12</v>
       </c>
     </row>
     <row r="146" ht="21" customHeight="1">
@@ -7130,21 +6596,17 @@
       <c r="K146" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L146" s="13">
-        <f>F146+I146+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C146,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M146" s="13">
-        <f>G146+J146-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C146,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N146" s="13">
-        <f>H146+K146+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C146,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O146" s="13">
-        <f>SUM(L146:N146)</f>
-        <v/>
+      <c r="L146" s="13" t="n">
+        <v>16030.23</v>
+      </c>
+      <c r="M146" s="13" t="n">
+        <v>-2708.05</v>
+      </c>
+      <c r="N146" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O146" s="13" t="n">
+        <v>13322.18</v>
       </c>
     </row>
     <row r="147" ht="21" customHeight="1">
@@ -7181,21 +6643,17 @@
       <c r="K147" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L147" s="13">
-        <f>F147+I147+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C147,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M147" s="13">
-        <f>G147+J147-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C147,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N147" s="13">
-        <f>H147+K147+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C147,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O147" s="13">
-        <f>SUM(L147:N147)</f>
-        <v/>
+      <c r="L147" s="13" t="n">
+        <v>36922.66</v>
+      </c>
+      <c r="M147" s="13" t="n">
+        <v>-15708.54</v>
+      </c>
+      <c r="N147" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O147" s="13" t="n">
+        <v>21214.12</v>
       </c>
     </row>
     <row r="148" ht="21" customHeight="1">
@@ -7232,21 +6690,17 @@
       <c r="K148" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L148" s="13">
-        <f>F148+I148+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C148,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M148" s="13">
-        <f>G148+J148-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C148,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N148" s="13">
-        <f>H148+K148+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C148,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O148" s="13">
-        <f>SUM(L148:N148)</f>
-        <v/>
+      <c r="L148" s="13" t="n">
+        <v>54613.05</v>
+      </c>
+      <c r="M148" s="13" t="n">
+        <v>-49057.45</v>
+      </c>
+      <c r="N148" s="13" t="n">
+        <v>83713.49000000001</v>
+      </c>
+      <c r="O148" s="13" t="n">
+        <v>89269.09000000001</v>
       </c>
     </row>
     <row r="149" ht="21" customHeight="1">
@@ -7283,21 +6737,17 @@
       <c r="K149" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L149" s="13">
-        <f>F149+I149+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C149,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M149" s="13">
-        <f>G149+J149-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C149,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N149" s="13">
-        <f>H149+K149+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C149,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O149" s="13">
-        <f>SUM(L149:N149)</f>
-        <v/>
+      <c r="L149" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M149" s="13" t="n">
+        <v>-101754.9</v>
+      </c>
+      <c r="N149" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O149" s="13" t="n">
+        <v>-101754.9</v>
       </c>
     </row>
     <row r="150" ht="21" customHeight="1">
@@ -7334,21 +6784,17 @@
       <c r="K150" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L150" s="13">
-        <f>F150+I150+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C150,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M150" s="13">
-        <f>G150+J150-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C150,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N150" s="13">
-        <f>H150+K150+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C150,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O150" s="13">
-        <f>SUM(L150:N150)</f>
-        <v/>
+      <c r="L150" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M150" s="13" t="n">
+        <v>-8664</v>
+      </c>
+      <c r="N150" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O150" s="13" t="n">
+        <v>-8664</v>
       </c>
     </row>
     <row r="151" ht="21" customHeight="1">
@@ -7385,21 +6831,17 @@
       <c r="K151" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L151" s="13">
-        <f>F151+I151+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C151,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M151" s="13">
-        <f>G151+J151-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C151,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N151" s="13">
-        <f>H151+K151+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C151,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O151" s="13">
-        <f>SUM(L151:N151)</f>
-        <v/>
+      <c r="L151" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M151" s="13" t="n">
+        <v>-16506.24</v>
+      </c>
+      <c r="N151" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O151" s="13" t="n">
+        <v>-16506.24</v>
       </c>
     </row>
     <row r="152" ht="21" customHeight="1">
@@ -7436,21 +6878,17 @@
       <c r="K152" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L152" s="13">
-        <f>F152+I152+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C152,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M152" s="13">
-        <f>G152+J152-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C152,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N152" s="13">
-        <f>H152+K152+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C152,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O152" s="13">
-        <f>SUM(L152:N152)</f>
-        <v/>
+      <c r="L152" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M152" s="13" t="n">
+        <v>-1342.17</v>
+      </c>
+      <c r="N152" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O152" s="13" t="n">
+        <v>-1342.17</v>
       </c>
     </row>
     <row r="153" ht="21" customHeight="1">
@@ -7487,21 +6925,17 @@
       <c r="K153" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L153" s="13">
-        <f>F153+I153+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C153,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M153" s="13">
-        <f>G153+J153-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C153,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N153" s="13">
-        <f>H153+K153+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C153,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O153" s="13">
-        <f>SUM(L153:N153)</f>
-        <v/>
+      <c r="L153" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M153" s="13" t="n">
+        <v>-7075.24</v>
+      </c>
+      <c r="N153" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O153" s="13" t="n">
+        <v>-7075.24</v>
       </c>
     </row>
     <row r="154" ht="21" customHeight="1">
@@ -7538,21 +6972,17 @@
       <c r="K154" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L154" s="13">
-        <f>F154+I154+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C154,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M154" s="13">
-        <f>G154+J154-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C154,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N154" s="13">
-        <f>H154+K154+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C154,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O154" s="13">
-        <f>SUM(L154:N154)</f>
-        <v/>
+      <c r="L154" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M154" s="13" t="n">
+        <v>-10291.6</v>
+      </c>
+      <c r="N154" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O154" s="13" t="n">
+        <v>-10291.6</v>
       </c>
     </row>
     <row r="155" ht="21" customHeight="1">
@@ -7589,21 +7019,17 @@
       <c r="K155" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L155" s="13">
-        <f>F155+I155+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C155,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M155" s="13">
-        <f>G155+J155-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C155,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N155" s="13">
-        <f>H155+K155+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C155,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O155" s="13">
-        <f>SUM(L155:N155)</f>
-        <v/>
+      <c r="L155" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M155" s="13" t="n">
+        <v>-10045.97</v>
+      </c>
+      <c r="N155" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O155" s="13" t="n">
+        <v>-10045.97</v>
       </c>
     </row>
     <row r="156" ht="21" customHeight="1">
@@ -7640,21 +7066,17 @@
       <c r="K156" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L156" s="13">
-        <f>F156+I156+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C156,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M156" s="13">
-        <f>G156+J156-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C156,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N156" s="13">
-        <f>H156+K156+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C156,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O156" s="13">
-        <f>SUM(L156:N156)</f>
-        <v/>
+      <c r="L156" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M156" s="13" t="n">
+        <v>-13211</v>
+      </c>
+      <c r="N156" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O156" s="13" t="n">
+        <v>-13211</v>
       </c>
     </row>
     <row r="157" ht="21" customHeight="1">
@@ -7691,21 +7113,17 @@
       <c r="K157" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L157" s="13">
-        <f>F157+I157+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C157,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M157" s="13">
-        <f>G157+J157-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C157,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N157" s="13">
-        <f>H157+K157+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C157,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O157" s="13">
-        <f>SUM(L157:N157)</f>
-        <v/>
+      <c r="L157" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M157" s="13" t="n">
+        <v>-1698.87</v>
+      </c>
+      <c r="N157" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O157" s="13" t="n">
+        <v>-1698.87</v>
       </c>
     </row>
     <row r="158" ht="21" customHeight="1">
@@ -7742,21 +7160,17 @@
       <c r="K158" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L158" s="13">
-        <f>F158+I158+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C158,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M158" s="13">
-        <f>G158+J158-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C158,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N158" s="13">
-        <f>H158+K158+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C158,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O158" s="13">
-        <f>SUM(L158:N158)</f>
-        <v/>
+      <c r="L158" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M158" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N158" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O158" s="13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="159" ht="21" customHeight="1">
@@ -7793,21 +7207,17 @@
       <c r="K159" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L159" s="13">
-        <f>F159+I159+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C159,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M159" s="13">
-        <f>G159+J159-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C159,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N159" s="13">
-        <f>H159+K159+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C159,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O159" s="13">
-        <f>SUM(L159:N159)</f>
-        <v/>
+      <c r="L159" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M159" s="13" t="n">
+        <v>-94648.47</v>
+      </c>
+      <c r="N159" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O159" s="13" t="n">
+        <v>-94648.47</v>
       </c>
     </row>
     <row r="160" ht="21" customHeight="1">
@@ -7844,21 +7254,17 @@
       <c r="K160" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L160" s="13">
-        <f>F160+I160+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C160,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M160" s="13">
-        <f>G160+J160-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C160,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N160" s="13">
-        <f>H160+K160+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C160,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O160" s="13">
-        <f>SUM(L160:N160)</f>
-        <v/>
+      <c r="L160" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M160" s="13" t="n">
+        <v>-2488</v>
+      </c>
+      <c r="N160" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O160" s="13" t="n">
+        <v>-2488</v>
       </c>
     </row>
     <row r="161" ht="21" customHeight="1">
@@ -7895,21 +7301,17 @@
       <c r="K161" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L161" s="13">
-        <f>F161+I161+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C161,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M161" s="13">
-        <f>G161+J161-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C161,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N161" s="13">
-        <f>H161+K161+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C161,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O161" s="13">
-        <f>SUM(L161:N161)</f>
-        <v/>
+      <c r="L161" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M161" s="13" t="n">
+        <v>-88828.60000000001</v>
+      </c>
+      <c r="N161" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O161" s="13" t="n">
+        <v>-88828.60000000001</v>
       </c>
     </row>
     <row r="162" ht="21" customHeight="1">
@@ -7946,21 +7348,17 @@
       <c r="K162" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L162" s="13">
-        <f>F162+I162+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C162,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M162" s="13">
-        <f>G162+J162-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C162,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N162" s="13">
-        <f>H162+K162+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C162,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O162" s="13">
-        <f>SUM(L162:N162)</f>
-        <v/>
+      <c r="L162" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M162" s="13" t="n">
+        <v>-11735.18</v>
+      </c>
+      <c r="N162" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O162" s="13" t="n">
+        <v>-11735.18</v>
       </c>
     </row>
     <row r="163" ht="21" customHeight="1">
@@ -7997,21 +7395,17 @@
       <c r="K163" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L163" s="13">
-        <f>F163+I163+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C163,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M163" s="13">
-        <f>G163+J163-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C163,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N163" s="13">
-        <f>H163+K163+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C163,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O163" s="13">
-        <f>SUM(L163:N163)</f>
-        <v/>
+      <c r="L163" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M163" s="13" t="n">
+        <v>-5317.15</v>
+      </c>
+      <c r="N163" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O163" s="13" t="n">
+        <v>-5317.15</v>
       </c>
     </row>
     <row r="164" ht="21" customHeight="1">
@@ -8048,21 +7442,17 @@
       <c r="K164" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L164" s="13">
-        <f>F164+I164+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C164,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M164" s="13">
-        <f>G164+J164-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C164,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N164" s="13">
-        <f>H164+K164+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C164,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O164" s="13">
-        <f>SUM(L164:N164)</f>
-        <v/>
+      <c r="L164" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M164" s="13" t="n">
+        <v>-30</v>
+      </c>
+      <c r="N164" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O164" s="13" t="n">
+        <v>-30</v>
       </c>
     </row>
     <row r="165" ht="21" customHeight="1">
@@ -8099,21 +7489,17 @@
       <c r="K165" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L165" s="13">
-        <f>F165+I165+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C165,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M165" s="13">
-        <f>G165+J165-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C165,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N165" s="13">
-        <f>H165+K165+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C165,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O165" s="13">
-        <f>SUM(L165:N165)</f>
-        <v/>
+      <c r="L165" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M165" s="13" t="n">
+        <v>-580</v>
+      </c>
+      <c r="N165" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O165" s="13" t="n">
+        <v>-580</v>
       </c>
     </row>
     <row r="166" ht="21" customHeight="1">
@@ -8150,21 +7536,17 @@
       <c r="K166" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L166" s="13">
-        <f>F166+I166+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C166,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M166" s="13">
-        <f>G166+J166-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C166,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N166" s="13">
-        <f>H166+K166+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C166,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O166" s="13">
-        <f>SUM(L166:N166)</f>
-        <v/>
+      <c r="L166" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M166" s="13" t="n">
+        <v>-7</v>
+      </c>
+      <c r="N166" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O166" s="13" t="n">
+        <v>-7</v>
       </c>
     </row>
     <row r="167" ht="21" customHeight="1">
@@ -8201,21 +7583,17 @@
       <c r="K167" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L167" s="13">
-        <f>F167+I167+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C167,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M167" s="13">
-        <f>G167+J167-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C167,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N167" s="13">
-        <f>H167+K167+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C167,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O167" s="13">
-        <f>SUM(L167:N167)</f>
-        <v/>
+      <c r="L167" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M167" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N167" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O167" s="13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="168" ht="21" customHeight="1">
@@ -8252,21 +7630,17 @@
       <c r="K168" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L168" s="13">
-        <f>F168+I168+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C168,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M168" s="13">
-        <f>G168+J168-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C168,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N168" s="13">
-        <f>H168+K168+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C168,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O168" s="13">
-        <f>SUM(L168:N168)</f>
-        <v/>
+      <c r="L168" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M168" s="13" t="n">
+        <v>-64851</v>
+      </c>
+      <c r="N168" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O168" s="13" t="n">
+        <v>-64851</v>
       </c>
     </row>
     <row r="169" ht="21" customHeight="1">
@@ -8303,21 +7677,17 @@
       <c r="K169" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L169" s="13">
-        <f>F169+I169+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C169,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M169" s="13">
-        <f>G169+J169-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C169,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N169" s="13">
-        <f>H169+K169+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C169,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O169" s="13">
-        <f>SUM(L169:N169)</f>
-        <v/>
+      <c r="L169" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M169" s="13" t="n">
+        <v>-8447.58</v>
+      </c>
+      <c r="N169" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O169" s="13" t="n">
+        <v>-8447.58</v>
       </c>
     </row>
     <row r="170" ht="21" customHeight="1">
@@ -8354,21 +7724,17 @@
       <c r="K170" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L170" s="13">
-        <f>F170+I170+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C170,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M170" s="13">
-        <f>G170+J170-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C170,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N170" s="13">
-        <f>H170+K170+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C170,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O170" s="13">
-        <f>SUM(L170:N170)</f>
-        <v/>
+      <c r="L170" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M170" s="13" t="n">
+        <v>-685.6799999999999</v>
+      </c>
+      <c r="N170" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O170" s="13" t="n">
+        <v>-685.6799999999999</v>
       </c>
     </row>
     <row r="171" ht="21" customHeight="1">
@@ -8405,21 +7771,17 @@
       <c r="K171" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L171" s="13">
-        <f>F171+I171+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C171,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M171" s="13">
-        <f>G171+J171-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C171,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N171" s="13">
-        <f>H171+K171+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C171,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O171" s="13">
-        <f>SUM(L171:N171)</f>
-        <v/>
+      <c r="L171" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M171" s="13" t="n">
+        <v>-6155.7</v>
+      </c>
+      <c r="N171" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O171" s="13" t="n">
+        <v>-6155.7</v>
       </c>
     </row>
     <row r="172" ht="21" customHeight="1">
@@ -8456,21 +7818,17 @@
       <c r="K172" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L172" s="13">
-        <f>F172+I172+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C172,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M172" s="13">
-        <f>G172+J172-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C172,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N172" s="13">
-        <f>H172+K172+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C172,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O172" s="13">
-        <f>SUM(L172:N172)</f>
-        <v/>
+      <c r="L172" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M172" s="13" t="n">
+        <v>-4555.48</v>
+      </c>
+      <c r="N172" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O172" s="13" t="n">
+        <v>-4555.48</v>
       </c>
     </row>
     <row r="173" ht="21" customHeight="1">
@@ -8507,21 +7865,17 @@
       <c r="K173" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L173" s="13">
-        <f>F173+I173+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C173,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M173" s="13">
-        <f>G173+J173-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C173,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N173" s="13">
-        <f>H173+K173+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C173,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O173" s="13">
-        <f>SUM(L173:N173)</f>
-        <v/>
+      <c r="L173" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M173" s="13" t="n">
+        <v>-652.87</v>
+      </c>
+      <c r="N173" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O173" s="13" t="n">
+        <v>-652.87</v>
       </c>
     </row>
     <row r="174" ht="21" customHeight="1">
@@ -8558,21 +7912,17 @@
       <c r="K174" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L174" s="13">
-        <f>F174+I174+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C174,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M174" s="13">
-        <f>G174+J174-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C174,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N174" s="13">
-        <f>H174+K174+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C174,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O174" s="13">
-        <f>SUM(L174:N174)</f>
-        <v/>
+      <c r="L174" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M174" s="13" t="n">
+        <v>-3195.76</v>
+      </c>
+      <c r="N174" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O174" s="13" t="n">
+        <v>-3195.76</v>
       </c>
     </row>
     <row r="175" ht="21" customHeight="1">
@@ -8609,21 +7959,17 @@
       <c r="K175" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L175" s="13">
-        <f>F175+I175+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C175,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M175" s="13">
-        <f>G175+J175-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C175,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N175" s="13">
-        <f>H175+K175+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C175,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O175" s="13">
-        <f>SUM(L175:N175)</f>
-        <v/>
+      <c r="L175" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M175" s="13" t="n">
+        <v>-555636.12</v>
+      </c>
+      <c r="N175" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O175" s="13" t="n">
+        <v>-555636.12</v>
       </c>
     </row>
     <row r="176" ht="21" customHeight="1">
@@ -8660,21 +8006,17 @@
       <c r="K176" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L176" s="13">
-        <f>F176+I176+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C176,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M176" s="13">
-        <f>G176+J176-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C176,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N176" s="13">
-        <f>H176+K176+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C176,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O176" s="13">
-        <f>SUM(L176:N176)</f>
-        <v/>
+      <c r="L176" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M176" s="13" t="n">
+        <v>-87966.71000000001</v>
+      </c>
+      <c r="N176" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O176" s="13" t="n">
+        <v>-87966.71000000001</v>
       </c>
     </row>
     <row r="177" ht="21" customHeight="1">
@@ -8711,21 +8053,17 @@
       <c r="K177" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L177" s="13">
-        <f>F177+I177+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C177,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M177" s="13">
-        <f>G177+J177-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C177,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N177" s="13">
-        <f>H177+K177+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C177,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O177" s="13">
-        <f>SUM(L177:N177)</f>
-        <v/>
+      <c r="L177" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M177" s="13" t="n">
+        <v>-990.37</v>
+      </c>
+      <c r="N177" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O177" s="13" t="n">
+        <v>-990.37</v>
       </c>
     </row>
     <row r="178" ht="21" customHeight="1">
@@ -8762,21 +8100,17 @@
       <c r="K178" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L178" s="13">
-        <f>F178+I178+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C178,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M178" s="13">
-        <f>G178+J178-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C178,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N178" s="13">
-        <f>H178+K178+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C178,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O178" s="13">
-        <f>SUM(L178:N178)</f>
-        <v/>
+      <c r="L178" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M178" s="13" t="n">
+        <v>-10.5</v>
+      </c>
+      <c r="N178" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O178" s="13" t="n">
+        <v>-10.5</v>
       </c>
     </row>
     <row r="179" ht="21" customHeight="1">
@@ -8813,21 +8147,17 @@
       <c r="K179" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L179" s="13">
-        <f>F179+I179+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C179,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M179" s="13">
-        <f>G179+J179-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C179,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N179" s="13">
-        <f>H179+K179+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C179,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O179" s="13">
-        <f>SUM(L179:N179)</f>
-        <v/>
+      <c r="L179" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M179" s="13" t="n">
+        <v>112.3</v>
+      </c>
+      <c r="N179" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O179" s="13" t="n">
+        <v>112.3</v>
       </c>
     </row>
     <row r="180" ht="21" customHeight="1">
@@ -8864,21 +8194,17 @@
       <c r="K180" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L180" s="13">
-        <f>F180+I180+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C180,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M180" s="13">
-        <f>G180+J180-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C180,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N180" s="13">
-        <f>H180+K180+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C180,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O180" s="13">
-        <f>SUM(L180:N180)</f>
-        <v/>
+      <c r="L180" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M180" s="13" t="n">
+        <v>-5539.21</v>
+      </c>
+      <c r="N180" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O180" s="13" t="n">
+        <v>-5539.21</v>
       </c>
     </row>
     <row r="181" ht="21" customHeight="1">
@@ -8915,21 +8241,17 @@
       <c r="K181" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L181" s="13">
-        <f>F181+I181+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C181,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M181" s="13">
-        <f>G181+J181-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C181,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N181" s="13">
-        <f>H181+K181+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C181,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O181" s="13">
-        <f>SUM(L181:N181)</f>
-        <v/>
+      <c r="L181" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M181" s="13" t="n">
+        <v>-19913.68</v>
+      </c>
+      <c r="N181" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O181" s="13" t="n">
+        <v>-19913.68</v>
       </c>
     </row>
     <row r="182" ht="21" customHeight="1">
@@ -8966,21 +8288,17 @@
       <c r="K182" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L182" s="13">
-        <f>F182+I182+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C182,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M182" s="13">
-        <f>G182+J182-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C182,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N182" s="13">
-        <f>H182+K182+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C182,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O182" s="13">
-        <f>SUM(L182:N182)</f>
-        <v/>
+      <c r="L182" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M182" s="13" t="n">
+        <v>-11348.78</v>
+      </c>
+      <c r="N182" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O182" s="13" t="n">
+        <v>-11348.78</v>
       </c>
     </row>
     <row r="183" ht="21" customHeight="1">
@@ -9017,21 +8335,17 @@
       <c r="K183" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L183" s="13">
-        <f>F183+I183+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C183,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M183" s="13">
-        <f>G183+J183-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C183,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N183" s="13">
-        <f>H183+K183+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C183,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O183" s="13">
-        <f>SUM(L183:N183)</f>
-        <v/>
+      <c r="L183" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M183" s="13" t="n">
+        <v>-13033.76</v>
+      </c>
+      <c r="N183" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O183" s="13" t="n">
+        <v>-13033.76</v>
       </c>
     </row>
     <row r="184" ht="21" customHeight="1">
@@ -9068,21 +8382,17 @@
       <c r="K184" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L184" s="13">
-        <f>F184+I184+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C184,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M184" s="13">
-        <f>G184+J184-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C184,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N184" s="13">
-        <f>H184+K184+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C184,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O184" s="13">
-        <f>SUM(L184:N184)</f>
-        <v/>
+      <c r="L184" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M184" s="13" t="n">
+        <v>-10779.28</v>
+      </c>
+      <c r="N184" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O184" s="13" t="n">
+        <v>-10779.28</v>
       </c>
     </row>
     <row r="185" ht="21" customHeight="1">
@@ -9119,21 +8429,17 @@
       <c r="K185" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L185" s="13">
-        <f>F185+I185+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C185,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M185" s="13">
-        <f>G185+J185-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C185,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N185" s="13">
-        <f>H185+K185+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C185,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O185" s="13">
-        <f>SUM(L185:N185)</f>
-        <v/>
+      <c r="L185" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M185" s="13" t="n">
+        <v>-761.1</v>
+      </c>
+      <c r="N185" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O185" s="13" t="n">
+        <v>-761.1</v>
       </c>
     </row>
     <row r="186" ht="21" customHeight="1">
@@ -9170,21 +8476,17 @@
       <c r="K186" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L186" s="13">
-        <f>F186+I186+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C186,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M186" s="13">
-        <f>G186+J186-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C186,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N186" s="13">
-        <f>H186+K186+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C186,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O186" s="13">
-        <f>SUM(L186:N186)</f>
-        <v/>
+      <c r="L186" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M186" s="13" t="n">
+        <v>-92999.39999999999</v>
+      </c>
+      <c r="N186" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O186" s="13" t="n">
+        <v>-92999.39999999999</v>
       </c>
     </row>
     <row r="187" ht="21" customHeight="1">
@@ -9221,21 +8523,17 @@
       <c r="K187" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L187" s="13">
-        <f>F187+I187+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C187,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M187" s="13">
-        <f>G187+J187-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C187,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N187" s="13">
-        <f>H187+K187+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C187,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O187" s="13">
-        <f>SUM(L187:N187)</f>
-        <v/>
+      <c r="L187" s="13" t="n">
+        <v>11272.5</v>
+      </c>
+      <c r="M187" s="13" t="n">
+        <v>-9792.09</v>
+      </c>
+      <c r="N187" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O187" s="13" t="n">
+        <v>1480.41</v>
       </c>
     </row>
     <row r="188" ht="21" customHeight="1">
@@ -9272,21 +8570,17 @@
       <c r="K188" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L188" s="13">
-        <f>F188+I188+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C188,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M188" s="13">
-        <f>G188+J188-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C188,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N188" s="13">
-        <f>H188+K188+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C188,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O188" s="13">
-        <f>SUM(L188:N188)</f>
-        <v/>
+      <c r="L188" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M188" s="13" t="n">
+        <v>-15481.18</v>
+      </c>
+      <c r="N188" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O188" s="13" t="n">
+        <v>-15481.18</v>
       </c>
     </row>
     <row r="189" ht="21" customHeight="1">
@@ -9323,21 +8617,17 @@
       <c r="K189" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L189" s="13">
-        <f>F189+I189+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C189,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M189" s="13">
-        <f>G189+J189-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C189,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N189" s="13">
-        <f>H189+K189+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C189,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O189" s="13">
-        <f>SUM(L189:N189)</f>
-        <v/>
+      <c r="L189" s="13" t="n">
+        <v>11153.42</v>
+      </c>
+      <c r="M189" s="13" t="n">
+        <v>-365.72</v>
+      </c>
+      <c r="N189" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O189" s="13" t="n">
+        <v>10787.7</v>
       </c>
     </row>
     <row r="190" ht="21" customHeight="1">
@@ -9374,21 +8664,17 @@
       <c r="K190" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L190" s="13">
-        <f>F190+I190+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C190,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M190" s="13">
-        <f>G190+J190-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C190,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N190" s="13">
-        <f>H190+K190+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C190,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O190" s="13">
-        <f>SUM(L190:N190)</f>
-        <v/>
+      <c r="L190" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M190" s="13" t="n">
+        <v>-9673.93</v>
+      </c>
+      <c r="N190" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O190" s="13" t="n">
+        <v>-9673.93</v>
       </c>
     </row>
     <row r="191" ht="21" customHeight="1">
@@ -9425,21 +8711,17 @@
       <c r="K191" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L191" s="13">
-        <f>F191+I191+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C191,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M191" s="13">
-        <f>G191+J191-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C191,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N191" s="13">
-        <f>H191+K191+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C191,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O191" s="13">
-        <f>SUM(L191:N191)</f>
-        <v/>
+      <c r="L191" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M191" s="13" t="n">
+        <v>-4628.19</v>
+      </c>
+      <c r="N191" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O191" s="13" t="n">
+        <v>-4628.19</v>
       </c>
     </row>
     <row r="192" ht="21" customHeight="1">
@@ -9476,21 +8758,17 @@
       <c r="K192" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L192" s="13">
-        <f>F192+I192+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C192,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M192" s="13">
-        <f>G192+J192-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C192,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N192" s="13">
-        <f>H192+K192+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C192,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O192" s="13">
-        <f>SUM(L192:N192)</f>
-        <v/>
+      <c r="L192" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M192" s="13" t="n">
+        <v>-15276.38</v>
+      </c>
+      <c r="N192" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O192" s="13" t="n">
+        <v>-15276.38</v>
       </c>
     </row>
     <row r="193" ht="21" customHeight="1">
@@ -9527,21 +8805,17 @@
       <c r="K193" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L193" s="13">
-        <f>F193+I193+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C193,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M193" s="13">
-        <f>G193+J193-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C193,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N193" s="13">
-        <f>H193+K193+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C193,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O193" s="13">
-        <f>SUM(L193:N193)</f>
-        <v/>
+      <c r="L193" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M193" s="13" t="n">
+        <v>-6913.67</v>
+      </c>
+      <c r="N193" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O193" s="13" t="n">
+        <v>-6913.67</v>
       </c>
     </row>
     <row r="194" ht="21" customHeight="1">
@@ -9578,21 +8852,17 @@
       <c r="K194" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L194" s="13">
-        <f>F194+I194+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C194,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M194" s="13">
-        <f>G194+J194-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C194,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N194" s="13">
-        <f>H194+K194+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C194,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O194" s="13">
-        <f>SUM(L194:N194)</f>
-        <v/>
+      <c r="L194" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M194" s="13" t="n">
+        <v>-8323.5</v>
+      </c>
+      <c r="N194" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O194" s="13" t="n">
+        <v>-8323.5</v>
       </c>
     </row>
     <row r="195" ht="21" customHeight="1">
@@ -9629,21 +8899,17 @@
       <c r="K195" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L195" s="13">
-        <f>F195+I195+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C195,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M195" s="13">
-        <f>G195+J195-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C195,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N195" s="13">
-        <f>H195+K195+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C195,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O195" s="13">
-        <f>SUM(L195:N195)</f>
-        <v/>
+      <c r="L195" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M195" s="13" t="n">
+        <v>-2396.61</v>
+      </c>
+      <c r="N195" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O195" s="13" t="n">
+        <v>-2396.61</v>
       </c>
     </row>
     <row r="196" ht="21" customHeight="1">
@@ -9680,21 +8946,17 @@
       <c r="K196" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L196" s="13">
-        <f>F196+I196+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C196,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M196" s="13">
-        <f>G196+J196-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C196,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N196" s="13">
-        <f>H196+K196+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C196,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O196" s="13">
-        <f>SUM(L196:N196)</f>
-        <v/>
+      <c r="L196" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M196" s="13" t="n">
+        <v>-7875</v>
+      </c>
+      <c r="N196" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O196" s="13" t="n">
+        <v>-7875</v>
       </c>
     </row>
     <row r="197" ht="21" customHeight="1">
@@ -9731,21 +8993,17 @@
       <c r="K197" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L197" s="13">
-        <f>F197+I197+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C197,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M197" s="13">
-        <f>G197+J197-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C197,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N197" s="13">
-        <f>H197+K197+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C197,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O197" s="13">
-        <f>SUM(L197:N197)</f>
-        <v/>
+      <c r="L197" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M197" s="13" t="n">
+        <v>-2570</v>
+      </c>
+      <c r="N197" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O197" s="13" t="n">
+        <v>-2570</v>
       </c>
     </row>
     <row r="198" ht="21" customHeight="1">
@@ -9782,21 +9040,17 @@
       <c r="K198" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L198" s="13">
-        <f>F198+I198+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C198,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M198" s="13">
-        <f>G198+J198-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C198,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N198" s="13">
-        <f>H198+K198+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C198,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O198" s="13">
-        <f>SUM(L198:N198)</f>
-        <v/>
+      <c r="L198" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M198" s="13" t="n">
+        <v>-778.71</v>
+      </c>
+      <c r="N198" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O198" s="13" t="n">
+        <v>-778.71</v>
       </c>
     </row>
     <row r="199" ht="21" customHeight="1">
@@ -9833,21 +9087,17 @@
       <c r="K199" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L199" s="13">
-        <f>F199+I199+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C199,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M199" s="13">
-        <f>G199+J199-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C199,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N199" s="13">
-        <f>H199+K199+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C199,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O199" s="13">
-        <f>SUM(L199:N199)</f>
-        <v/>
+      <c r="L199" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M199" s="13" t="n">
+        <v>-34906.06</v>
+      </c>
+      <c r="N199" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O199" s="13" t="n">
+        <v>-34906.06</v>
       </c>
     </row>
     <row r="200" ht="21" customHeight="1">
@@ -9884,21 +9134,17 @@
       <c r="K200" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L200" s="13">
-        <f>F200+I200+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C200,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M200" s="13">
-        <f>G200+J200-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C200,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N200" s="13">
-        <f>H200+K200+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C200,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O200" s="13">
-        <f>SUM(L200:N200)</f>
-        <v/>
+      <c r="L200" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M200" s="13" t="n">
+        <v>-54513.8</v>
+      </c>
+      <c r="N200" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O200" s="13" t="n">
+        <v>-54513.8</v>
       </c>
     </row>
     <row r="201" ht="21" customHeight="1">
@@ -9935,21 +9181,17 @@
       <c r="K201" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L201" s="13">
-        <f>F201+I201+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C201,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M201" s="13">
-        <f>G201+J201-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C201,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N201" s="13">
-        <f>H201+K201+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C201,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O201" s="13">
-        <f>SUM(L201:N201)</f>
-        <v/>
+      <c r="L201" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M201" s="13" t="n">
+        <v>-15640.24</v>
+      </c>
+      <c r="N201" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O201" s="13" t="n">
+        <v>-15640.24</v>
       </c>
     </row>
     <row r="202" ht="21" customHeight="1">
@@ -9986,21 +9228,17 @@
       <c r="K202" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L202" s="13">
-        <f>F202+I202+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C202,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M202" s="13">
-        <f>G202+J202-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C202,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N202" s="13">
-        <f>H202+K202+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C202,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O202" s="13">
-        <f>SUM(L202:N202)</f>
-        <v/>
+      <c r="L202" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M202" s="13" t="n">
+        <v>-6616.91</v>
+      </c>
+      <c r="N202" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O202" s="13" t="n">
+        <v>-6616.91</v>
       </c>
     </row>
     <row r="203" ht="21" customHeight="1">
@@ -10037,21 +9275,17 @@
       <c r="K203" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L203" s="13">
-        <f>F203+I203+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C203,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M203" s="13">
-        <f>G203+J203-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C203,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N203" s="13">
-        <f>H203+K203+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C203,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O203" s="13">
-        <f>SUM(L203:N203)</f>
-        <v/>
+      <c r="L203" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M203" s="13" t="n">
+        <v>-3949</v>
+      </c>
+      <c r="N203" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O203" s="13" t="n">
+        <v>-3949</v>
       </c>
     </row>
     <row r="204" ht="21" customHeight="1">
@@ -10076,21 +9310,17 @@
       <c r="K204" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L204" s="13">
-        <f>F204+I204+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C204,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M204" s="13">
-        <f>G204+J204-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C204,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N204" s="13">
-        <f>H204+K204+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C204,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O204" s="13">
-        <f>SUM(L204:N204)</f>
-        <v/>
+      <c r="L204" s="13" t="n">
+        <v>-128.47</v>
+      </c>
+      <c r="M204" s="13" t="n">
+        <v>-3256845.05</v>
+      </c>
+      <c r="N204" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O204" s="13" t="n">
+        <v>-3256973.52</v>
       </c>
     </row>
     <row r="205" ht="21" customHeight="1">
@@ -10119,21 +9349,17 @@
       <c r="K205" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L205" s="13">
-        <f>F205+I205+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C205,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M205" s="13">
-        <f>G205+J205-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C205,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N205" s="13">
-        <f>H205+K205+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C205,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O205" s="13">
-        <f>SUM(L205:N205)</f>
-        <v/>
+      <c r="L205" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M205" s="13" t="n">
+        <v>-1187.54</v>
+      </c>
+      <c r="N205" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O205" s="13" t="n">
+        <v>-1187.54</v>
       </c>
     </row>
     <row r="206" ht="21" customHeight="1">
@@ -10162,21 +9388,17 @@
       <c r="K206" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L206" s="13">
-        <f>F206+I206+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C206,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M206" s="13">
-        <f>G206+J206-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C206,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N206" s="13">
-        <f>H206+K206+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C206,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O206" s="13">
-        <f>SUM(L206:N206)</f>
-        <v/>
+      <c r="L206" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M206" s="13" t="n">
+        <v>-2192.04</v>
+      </c>
+      <c r="N206" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O206" s="13" t="n">
+        <v>-2192.04</v>
       </c>
     </row>
     <row r="207" ht="21" customHeight="1">
@@ -10205,21 +9427,17 @@
       <c r="K207" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L207" s="13">
-        <f>F207+I207+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C207,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M207" s="13">
-        <f>G207+J207-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C207,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N207" s="13">
-        <f>H207+K207+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C207,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O207" s="13">
-        <f>SUM(L207:N207)</f>
-        <v/>
+      <c r="L207" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M207" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N207" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O207" s="13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="208" ht="21" customHeight="1">
@@ -10248,21 +9466,17 @@
       <c r="K208" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L208" s="13">
-        <f>F208+I208+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C208,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M208" s="13">
-        <f>G208+J208-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C208,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N208" s="13">
-        <f>H208+K208+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C208,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O208" s="13">
-        <f>SUM(L208:N208)</f>
-        <v/>
+      <c r="L208" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M208" s="13" t="n">
+        <v>-1002.99</v>
+      </c>
+      <c r="N208" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O208" s="13" t="n">
+        <v>-1002.99</v>
       </c>
     </row>
     <row r="209" ht="21" customHeight="1">
@@ -10291,21 +9505,17 @@
       <c r="K209" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L209" s="13">
-        <f>F209+I209+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C209,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M209" s="13">
-        <f>G209+J209-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C209,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N209" s="13">
-        <f>H209+K209+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C209,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O209" s="13">
-        <f>SUM(L209:N209)</f>
-        <v/>
+      <c r="L209" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M209" s="13" t="n">
+        <v>-349.4</v>
+      </c>
+      <c r="N209" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O209" s="13" t="n">
+        <v>-349.4</v>
       </c>
     </row>
     <row r="210" ht="21" customHeight="1">
@@ -10334,21 +9544,17 @@
       <c r="K210" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L210" s="13">
-        <f>F210+I210+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C210,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M210" s="13">
-        <f>G210+J210-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C210,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N210" s="13">
-        <f>H210+K210+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C210,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O210" s="13">
-        <f>SUM(L210:N210)</f>
-        <v/>
+      <c r="L210" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M210" s="13" t="n">
+        <v>-77.84999999999999</v>
+      </c>
+      <c r="N210" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O210" s="13" t="n">
+        <v>-77.84999999999999</v>
       </c>
     </row>
     <row r="211" ht="21" customHeight="1">
@@ -10377,21 +9583,17 @@
       <c r="K211" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L211" s="13">
-        <f>F211+I211+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C211,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M211" s="13">
-        <f>G211+J211-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C211,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N211" s="13">
-        <f>H211+K211+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C211,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O211" s="13">
-        <f>SUM(L211:N211)</f>
-        <v/>
+      <c r="L211" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M211" s="13" t="n">
+        <v>-33.46</v>
+      </c>
+      <c r="N211" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O211" s="13" t="n">
+        <v>-33.46</v>
       </c>
     </row>
     <row r="212" ht="21" customHeight="1">
@@ -10420,21 +9622,17 @@
       <c r="K212" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L212" s="13">
-        <f>F212+I212+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C212,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M212" s="13">
-        <f>G212+J212-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C212,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N212" s="13">
-        <f>H212+K212+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C212,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O212" s="13">
-        <f>SUM(L212:N212)</f>
-        <v/>
+      <c r="L212" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M212" s="13" t="n">
+        <v>-180.18</v>
+      </c>
+      <c r="N212" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O212" s="13" t="n">
+        <v>-180.18</v>
       </c>
     </row>
     <row r="213" ht="21" customHeight="1">
@@ -10463,21 +9661,17 @@
       <c r="K213" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L213" s="13">
-        <f>F213+I213+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C213,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M213" s="13">
-        <f>G213+J213-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C213,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N213" s="13">
-        <f>H213+K213+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C213,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O213" s="13">
-        <f>SUM(L213:N213)</f>
-        <v/>
+      <c r="L213" s="13" t="n">
+        <v>9367.07</v>
+      </c>
+      <c r="M213" s="13" t="n">
+        <v>-5289.44</v>
+      </c>
+      <c r="N213" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O213" s="13" t="n">
+        <v>4077.63</v>
       </c>
     </row>
     <row r="214" ht="21" customHeight="1">
@@ -10506,21 +9700,17 @@
       <c r="K214" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L214" s="13">
-        <f>F214+I214+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C214,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M214" s="13">
-        <f>G214+J214-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C214,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N214" s="13">
-        <f>H214+K214+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C214,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O214" s="13">
-        <f>SUM(L214:N214)</f>
-        <v/>
+      <c r="L214" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M214" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N214" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O214" s="13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="215" ht="21" customHeight="1">
@@ -10549,21 +9739,17 @@
       <c r="K215" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L215" s="13">
-        <f>F215+I215+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C215,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M215" s="13">
-        <f>G215+J215-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C215,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N215" s="13">
-        <f>H215+K215+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C215,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O215" s="13">
-        <f>SUM(L215:N215)</f>
-        <v/>
+      <c r="L215" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M215" s="13" t="n">
+        <v>-177.57</v>
+      </c>
+      <c r="N215" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O215" s="13" t="n">
+        <v>-177.57</v>
       </c>
     </row>
     <row r="216" ht="21" customHeight="1">
@@ -10592,21 +9778,17 @@
       <c r="K216" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L216" s="13">
-        <f>F216+I216+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C216,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M216" s="13">
-        <f>G216+J216-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C216,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N216" s="13">
-        <f>H216+K216+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C216,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O216" s="13">
-        <f>SUM(L216:N216)</f>
-        <v/>
+      <c r="L216" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M216" s="13" t="n">
+        <v>-2162</v>
+      </c>
+      <c r="N216" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O216" s="13" t="n">
+        <v>-2162</v>
       </c>
     </row>
     <row r="217" ht="21" customHeight="1">
@@ -10635,21 +9817,17 @@
       <c r="K217" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L217" s="13">
-        <f>F217+I217+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C217,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M217" s="13">
-        <f>G217+J217-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C217,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N217" s="13">
-        <f>H217+K217+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C217,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O217" s="13">
-        <f>SUM(L217:N217)</f>
-        <v/>
+      <c r="L217" s="13" t="n">
+        <v>13000</v>
+      </c>
+      <c r="M217" s="13" t="n">
+        <v>-6383.76</v>
+      </c>
+      <c r="N217" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O217" s="13" t="n">
+        <v>6616.24</v>
       </c>
     </row>
     <row r="218" ht="21" customHeight="1">
@@ -10678,21 +9856,17 @@
       <c r="K218" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L218" s="13">
-        <f>F218+I218+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C218,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M218" s="13">
-        <f>G218+J218-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C218,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N218" s="13">
-        <f>H218+K218+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C218,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O218" s="13">
-        <f>SUM(L218:N218)</f>
-        <v/>
+      <c r="L218" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M218" s="13" t="n">
+        <v>-1010</v>
+      </c>
+      <c r="N218" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O218" s="13" t="n">
+        <v>-1010</v>
       </c>
     </row>
     <row r="219" ht="21" customHeight="1">
@@ -10721,21 +9895,17 @@
       <c r="K219" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L219" s="13">
-        <f>F219+I219+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C219,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M219" s="13">
-        <f>G219+J219-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C219,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N219" s="13">
-        <f>H219+K219+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C219,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O219" s="13">
-        <f>SUM(L219:N219)</f>
-        <v/>
+      <c r="L219" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M219" s="13" t="n">
+        <v>-65.02</v>
+      </c>
+      <c r="N219" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O219" s="13" t="n">
+        <v>-65.02</v>
       </c>
     </row>
     <row r="220" ht="21" customHeight="1">
@@ -10764,21 +9934,17 @@
       <c r="K220" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L220" s="13">
-        <f>F220+I220+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C220,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M220" s="13">
-        <f>G220+J220-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C220,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N220" s="13">
-        <f>H220+K220+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C220,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O220" s="13">
-        <f>SUM(L220:N220)</f>
-        <v/>
+      <c r="L220" s="13" t="n">
+        <v>40500</v>
+      </c>
+      <c r="M220" s="13" t="n">
+        <v>-21238.51</v>
+      </c>
+      <c r="N220" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O220" s="13" t="n">
+        <v>19261.49</v>
       </c>
     </row>
     <row r="221" ht="21" customHeight="1">
@@ -10807,21 +9973,17 @@
       <c r="K221" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L221" s="13">
-        <f>F221+I221+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C221,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M221" s="13">
-        <f>G221+J221-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C221,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N221" s="13">
-        <f>H221+K221+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C221,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O221" s="13">
-        <f>SUM(L221:N221)</f>
-        <v/>
+      <c r="L221" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M221" s="13" t="n">
+        <v>-79.34</v>
+      </c>
+      <c r="N221" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O221" s="13" t="n">
+        <v>-79.34</v>
       </c>
     </row>
     <row r="222" ht="21" customHeight="1">
@@ -10850,23 +10012,21 @@
       <c r="K222" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L222" s="13">
-        <f>F222+I222+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C222,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="M222" s="13">
-        <f>G222+J222-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C222,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="N222" s="13">
-        <f>H222+K222+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$126,'[FC Eingabe.xlsx]FC Eingabe'!$F$7:$F$126,C222,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$126,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="O222" s="13">
-        <f>SUM(L222:N222)</f>
-        <v/>
-      </c>
-    </row>
+      <c r="L222" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M222" s="13" t="n">
+        <v>-3282.09</v>
+      </c>
+      <c r="N222" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O222" s="13" t="n">
+        <v>-3282.09</v>
+      </c>
+    </row>
+    <row r="223"/>
+    <row r="224"/>
     <row r="225">
       <c r="C225" t="inlineStr">
         <is>
